--- a/docs/lanafood_menu.xlsx
+++ b/docs/lanafood_menu.xlsx
@@ -27,147 +27,156 @@
     <t>Display Order</t>
   </si>
   <si>
+    <t>Subcategory</t>
+  </si>
+  <si>
     <t>Holiday Menu</t>
   </si>
   <si>
+    <t>Name</t>
+  </si>
+  <si>
     <t>Праздничное меню</t>
   </si>
   <si>
+    <t>Group</t>
+  </si>
+  <si>
+    <t>Group ID</t>
+  </si>
+  <si>
     <t>Everyday Menu</t>
   </si>
   <si>
+    <t>Rolls</t>
+  </si>
+  <si>
     <t>Основное меню</t>
   </si>
   <si>
+    <t>Variant</t>
+  </si>
+  <si>
     <t>Kids' Menu</t>
   </si>
   <si>
     <t>Детское меню</t>
   </si>
   <si>
+    <t>Quantity</t>
+  </si>
+  <si>
+    <t>Holiday Salads</t>
+  </si>
+  <si>
+    <t>Quantity Unit</t>
+  </si>
+  <si>
     <t>GastroBoxes</t>
   </si>
   <si>
     <t>Гастробоксы</t>
   </si>
   <si>
-    <t>Subcategory</t>
-  </si>
-  <si>
-    <t>Rolls</t>
-  </si>
-  <si>
-    <t>Holiday Salads</t>
-  </si>
-  <si>
     <t>Blinchiki</t>
   </si>
   <si>
+    <t>Weight</t>
+  </si>
+  <si>
     <t>Homemade Treats</t>
   </si>
   <si>
+    <t>Weight Unit</t>
+  </si>
+  <si>
     <t>Hot Dishes</t>
   </si>
   <si>
+    <t>Price</t>
+  </si>
+  <si>
+    <t>Currency</t>
+  </si>
+  <si>
     <t>Appetizers</t>
   </si>
   <si>
+    <t>Description</t>
+  </si>
+  <si>
+    <t>Ingredients</t>
+  </si>
+  <si>
+    <t>Allergens</t>
+  </si>
+  <si>
+    <t>Photo</t>
+  </si>
+  <si>
     <t>Canapes in Cups</t>
   </si>
   <si>
-    <t>Name</t>
-  </si>
-  <si>
-    <t>Group</t>
-  </si>
-  <si>
-    <t>Group ID</t>
-  </si>
-  <si>
-    <t>Variant</t>
+    <t>Display Order in Subcategory</t>
+  </si>
+  <si>
+    <t>Published</t>
+  </si>
+  <si>
+    <t>Featured</t>
   </si>
   <si>
     <t>Soups</t>
   </si>
   <si>
-    <t>Quantity</t>
-  </si>
-  <si>
-    <t>Quantity Unit</t>
+    <t>Available</t>
   </si>
   <si>
     <t>Salads</t>
   </si>
   <si>
-    <t>Weight</t>
+    <t>Subcategory RU</t>
   </si>
   <si>
     <t>Main Dishes</t>
   </si>
   <si>
-    <t>Weight Unit</t>
-  </si>
-  <si>
-    <t>Price</t>
+    <t>Name RU</t>
+  </si>
+  <si>
+    <t>Description RU</t>
   </si>
   <si>
     <t>Baked Dishes</t>
   </si>
   <si>
-    <t>Currency</t>
-  </si>
-  <si>
-    <t>Description</t>
-  </si>
-  <si>
-    <t>Ingredients</t>
-  </si>
-  <si>
-    <t>Allergens</t>
-  </si>
-  <si>
-    <t>Photo</t>
+    <t>Ingredients RU</t>
+  </si>
+  <si>
+    <t>Variant RU</t>
   </si>
   <si>
     <t>Side Dishes</t>
   </si>
   <si>
-    <t>Display Order in Subcategory</t>
-  </si>
-  <si>
-    <t>Published</t>
+    <t>Cheese with Olives, Paprika and Ham</t>
   </si>
   <si>
     <t>Potato Dishes</t>
   </si>
   <si>
-    <t>Featured</t>
-  </si>
-  <si>
-    <t>Available</t>
-  </si>
-  <si>
-    <t>Subcategory RU</t>
-  </si>
-  <si>
-    <t>Name RU</t>
-  </si>
-  <si>
-    <t>Description RU</t>
-  </si>
-  <si>
-    <t>Ingredients RU</t>
-  </si>
-  <si>
-    <t>Variant RU</t>
-  </si>
-  <si>
-    <t>Cheese with Olives, Paprika and Ham</t>
+    <t>Syrniki</t>
   </si>
   <si>
     <t>pcs</t>
   </si>
   <si>
+    <t>syrniki</t>
+  </si>
+  <si>
+    <t>Classic</t>
+  </si>
+  <si>
     <t>lb</t>
   </si>
   <si>
@@ -177,79 +186,313 @@
     <t>cheese-olives.jpg</t>
   </si>
   <si>
+    <t>Farmer's cheese pancakes</t>
+  </si>
+  <si>
+    <t>farmer's cheese, eggs, flour, butter</t>
+  </si>
+  <si>
+    <t>сlassic-syrniki.jpg</t>
+  </si>
+  <si>
     <t>Zucchini Roll with Tomatoes</t>
   </si>
   <si>
+    <t>Домашние угощения</t>
+  </si>
+  <si>
+    <t>Сырники обычные</t>
+  </si>
+  <si>
+    <t>творог, яйца, мука , масло</t>
+  </si>
+  <si>
+    <t>Gluten-Free</t>
+  </si>
+  <si>
     <t>zucchini-tomatoes.jpg</t>
   </si>
   <si>
-    <t>Syrniki</t>
-  </si>
-  <si>
-    <t>syrniki</t>
-  </si>
-  <si>
-    <t>Classic</t>
-  </si>
-  <si>
     <t>Spinach with Salmon and Cream Cheese</t>
   </si>
   <si>
-    <t>Farmer's cheese pancakes</t>
-  </si>
-  <si>
-    <t>farmer's cheese, eggs, flour, butter</t>
-  </si>
-  <si>
-    <t>сlassic-syrniki.jpg</t>
+    <t>Сырники без глютена</t>
   </si>
   <si>
     <t>spinach-salmon-creamcheese.jpg</t>
   </si>
   <si>
-    <t>Домашние угощения</t>
-  </si>
-  <si>
-    <t>Сырники обычные</t>
-  </si>
-  <si>
-    <t>творог, яйца, мука , масло</t>
+    <t>with Raisins</t>
+  </si>
+  <si>
+    <t>farmer's cheese, eggs, flour, butter, raisins</t>
   </si>
   <si>
     <t>Carrot and Cheese with Shrimp, Cream Cheese and Herbs</t>
   </si>
   <si>
-    <t>Gluten-Free</t>
+    <t>Сырники с изюмом</t>
+  </si>
+  <si>
+    <t>творог, яйца, мука , масло, изюм</t>
   </si>
   <si>
     <t>carrot-cheese-shrimp.jpg</t>
   </si>
   <si>
-    <t>Сырники без глютена</t>
+    <t>Salted with Herbs</t>
   </si>
   <si>
     <t>Mushroom Clearing</t>
   </si>
   <si>
-    <t>with Raisins</t>
-  </si>
-  <si>
-    <t>farmer's cheese, eggs, flour, butter, raisins</t>
+    <t>Сырники с солью и зеленью</t>
   </si>
   <si>
     <t>chicken fillet, potatoes, carrots, egg, pickled cucumber, honey mushrooms, greens</t>
   </si>
   <si>
-    <t>Сырники с изюмом</t>
-  </si>
-  <si>
-    <t>творог, яйца, мука , масло, изюм</t>
+    <t>with Chia Seed</t>
   </si>
   <si>
     <t>mushroom-clearing.jpg</t>
   </si>
   <si>
-    <t>Salted with Herbs</t>
+    <t>Salad with Tongue</t>
+  </si>
+  <si>
+    <t>Сырники с семенами чиа</t>
+  </si>
+  <si>
+    <t>Cottage Cheese Casserole</t>
+  </si>
+  <si>
+    <t>tongue, eggs, cheese, cucumbers, potatoes, vegetables , carrots, mayonnaise</t>
+  </si>
+  <si>
+    <t>salad-tongue.jpg</t>
+  </si>
+  <si>
+    <t>cottagecheese-casserole.jpg</t>
+  </si>
+  <si>
+    <t>Tiffany</t>
+  </si>
+  <si>
+    <t>Запеканка из творога</t>
+  </si>
+  <si>
+    <t>Apple Charlotte Cake</t>
+  </si>
+  <si>
+    <t>boiled beef, nuts, eggs, mayonnaise, cheese, grapes</t>
+  </si>
+  <si>
+    <t>tiffany.jpg</t>
+  </si>
+  <si>
+    <t>apples, sugar, flour, vanilla, eggs</t>
+  </si>
+  <si>
+    <t>sharlotka.jpg</t>
+  </si>
+  <si>
+    <t>Herring under a Fur Coat (Seledka por shuboi)</t>
+  </si>
+  <si>
+    <t>Шарлотка</t>
+  </si>
+  <si>
+    <t>яблоки, сахар, мука, ванилин, яйца</t>
+  </si>
+  <si>
+    <t>herring, beets, potatoes, carrots, eggs, mayonnaise</t>
+  </si>
+  <si>
+    <t>Crepes</t>
+  </si>
+  <si>
+    <t>herring-fur-coat.jpg</t>
+  </si>
+  <si>
+    <t>crepes</t>
+  </si>
+  <si>
+    <t>eggs, milk, flour, butter, sugar, salt, vanilla</t>
+  </si>
+  <si>
+    <t>Beef and Mushrooms Salad</t>
+  </si>
+  <si>
+    <t>crepes.jpg</t>
+  </si>
+  <si>
+    <t>Блины</t>
+  </si>
+  <si>
+    <t>chicken, apples, celey, mustard dressing</t>
+  </si>
+  <si>
+    <t>яйца, молоко, мука, масло, сахар, соль, ванилин</t>
+  </si>
+  <si>
+    <t>beef-mushrooms-salad.jpg</t>
+  </si>
+  <si>
+    <t>with Cottage Cheese</t>
+  </si>
+  <si>
+    <t>Apple Salad</t>
+  </si>
+  <si>
+    <t>farmer's cheese, eggs, milk, flour, butter, sugar, salt, vanilla</t>
+  </si>
+  <si>
+    <t>crepes-cottage-cheese.jpg</t>
+  </si>
+  <si>
+    <t>apple-salad.jpg</t>
+  </si>
+  <si>
+    <t>Блины с творогом</t>
+  </si>
+  <si>
+    <t>творог, яйца, молоко, мука, масло, сахар, соль, ванилин</t>
+  </si>
+  <si>
+    <t>Mexican Tortilla with Cream Cheese, Salmon and Herbs</t>
+  </si>
+  <si>
+    <t>with Chicken</t>
+  </si>
+  <si>
+    <t>chicken, eggs, milk, flour, butter, sugar, salt, broth, seasonings</t>
+  </si>
+  <si>
+    <t>mexican-tortilla-salmon.jpg</t>
+  </si>
+  <si>
+    <t>Блины с курицей</t>
+  </si>
+  <si>
+    <t>курица, яйца, молоко, мука, масло, сахар, соль, бульон, специи</t>
+  </si>
+  <si>
+    <t>Mini Syrniki with a Pattern</t>
+  </si>
+  <si>
+    <t>with Beef</t>
+  </si>
+  <si>
+    <t>mini-syrniki.jpg</t>
+  </si>
+  <si>
+    <t>beef, eggs, milk, flour, butter, sugar, salt, broth, seasonings</t>
+  </si>
+  <si>
+    <t>Blinchiki with Spinach, Salmon, and Cream Cheese</t>
+  </si>
+  <si>
+    <t>Блины с говядиной</t>
+  </si>
+  <si>
+    <t>говядина, яйца, молоко, мука, масло, сахар, соль, бульон, специи</t>
+  </si>
+  <si>
+    <t>with Smoked Salmon</t>
+  </si>
+  <si>
+    <t>blinchiki-salmon-spinach-creamcheese.jpg</t>
+  </si>
+  <si>
+    <t>cream cheese, salmon, fresh herbs, flour, milk, eggs, salt, sugar</t>
+  </si>
+  <si>
+    <t>Binchiki with Salmon, Cream Cheese and Greens</t>
+  </si>
+  <si>
+    <t>Блины с лососем</t>
+  </si>
+  <si>
+    <t>крем-чиз, лосось, зелень, мука, молоко, яйца, соль, сахар</t>
+  </si>
+  <si>
+    <t>blinchiki-salmon-creamcheese.jpg</t>
+  </si>
+  <si>
+    <t>with Apples</t>
+  </si>
+  <si>
+    <t>apples, eggs, milk, flour, butter, sugar, salt, vanilla</t>
+  </si>
+  <si>
+    <t>Blinchiki with Mushrooms</t>
+  </si>
+  <si>
+    <t>Блины с яблоками</t>
+  </si>
+  <si>
+    <t>яблоки, яйца, молоко, мука, масло, сахар, соль, ванилин</t>
+  </si>
+  <si>
+    <t>blinchiki-mushrooms.jpg</t>
+  </si>
+  <si>
+    <t>with Mushrooms</t>
+  </si>
+  <si>
+    <t>mushrooms, eggs, milk, flour, butter, sugar, salt, sour cream</t>
+  </si>
+  <si>
+    <t>Blinchiki with Apple</t>
+  </si>
+  <si>
+    <t>Блины с грибами</t>
+  </si>
+  <si>
+    <t>грибы, яйца, молоко, мука, масло, сахар, соль, сметана</t>
+  </si>
+  <si>
+    <t>Borscht</t>
+  </si>
+  <si>
+    <t>borscht</t>
+  </si>
+  <si>
+    <t>Chicken</t>
+  </si>
+  <si>
+    <t>liter</t>
+  </si>
+  <si>
+    <t>chicken, beets, potatoes, onion, carrots, garlic, seasonings, sugar, vinegar</t>
+  </si>
+  <si>
+    <t>borscht.jpg</t>
+  </si>
+  <si>
+    <t>blinchiki-apple.jpg</t>
+  </si>
+  <si>
+    <t>Супы</t>
+  </si>
+  <si>
+    <t>Борщ с курицей</t>
+  </si>
+  <si>
+    <t>курица, свекла, картофель, лук, морковь, чеснок, специи, сахар, уксус</t>
+  </si>
+  <si>
+    <t>Mushroom Julienne in Tartlets</t>
+  </si>
+  <si>
+    <t>Beef</t>
+  </si>
+  <si>
+    <t>beef, beets, potatoes, onion, carrots, garlic, seasonings, sugar, vinegar</t>
+  </si>
+  <si>
+    <t>mushroom-julienne-tartlets.jpg</t>
   </si>
   <si>
     <t>Children's Menu</t>
@@ -258,610 +501,367 @@
     <t>Mini Burgers</t>
   </si>
   <si>
-    <t>Salad with Tongue</t>
-  </si>
-  <si>
-    <t>mini-burgers.jpg</t>
-  </si>
-  <si>
-    <t>tongue, eggs, cheese, cucumbers, potatoes, vegetables , carrots, mayonnaise</t>
-  </si>
-  <si>
-    <t>Сырники с солью и зеленью</t>
-  </si>
-  <si>
-    <t>salad-tongue.jpg</t>
+    <t>Борщ с говядиной</t>
+  </si>
+  <si>
+    <t>говядина, свекла, картофель, лук, морковь, чеснок, специи, сахар, уксус</t>
+  </si>
+  <si>
+    <t>Pancake Bags with Julienne</t>
+  </si>
+  <si>
+    <t>mini-burger.jpg</t>
+  </si>
+  <si>
+    <t>Sorrel Soup with Beef</t>
   </si>
   <si>
     <t>Wieners in dough</t>
   </si>
   <si>
-    <t>with Chia Seed</t>
+    <t>sorrel, beef, potatoes, eggs, onion, carrots, garlic, seasonings, sugar</t>
+  </si>
+  <si>
+    <t>sorrel-soup.jpg</t>
+  </si>
+  <si>
+    <t>pancake-julienne.jpg</t>
   </si>
   <si>
     <t>wieners-in-dough.jpg</t>
   </si>
   <si>
-    <t>Tiffany</t>
+    <t>Щавелевый с говядиной</t>
+  </si>
+  <si>
+    <t>щавель, говядина, картофель, яйца, лук, морковь, чеснок, специи, сахар</t>
+  </si>
+  <si>
+    <t>Profittroles with Ice Cream Fruit</t>
   </si>
   <si>
     <t>Profiteroles</t>
   </si>
   <si>
-    <t>boiled beef, nuts, eggs, mayonnaise, cheese, grapes</t>
-  </si>
-  <si>
-    <t>Сырники с семенами чиа</t>
-  </si>
-  <si>
-    <t>tiffany.jpg</t>
+    <t>Chicken Meatball Soup</t>
+  </si>
+  <si>
+    <t>with Rice</t>
   </si>
   <si>
     <t>profiteroles.jpg</t>
   </si>
   <si>
-    <t>Cottage Cheese Casserole</t>
+    <t>profittroles-icecream-fruit.jpg</t>
+  </si>
+  <si>
+    <t>ground chicken, potatoes, onion, carrots, garlic, seasonings, vermicelli</t>
   </si>
   <si>
     <t>Eclairs</t>
   </si>
   <si>
-    <t>Herring under a Fur Coat (Seledka por shuboi)</t>
-  </si>
-  <si>
-    <t>cottagecheese-casserole.jpg</t>
+    <t>chicken-meatball-soup.jpg</t>
+  </si>
+  <si>
+    <t>Baked Wheat Tarts with Tomato and Mozzarella Cheese</t>
   </si>
   <si>
     <t>eclairs.jpg</t>
   </si>
   <si>
-    <t>Запеканка из творога</t>
-  </si>
-  <si>
-    <t>herring, beets, potatoes, carrots, eggs, mayonnaise</t>
-  </si>
-  <si>
-    <t>herring-fur-coat.jpg</t>
-  </si>
-  <si>
-    <t>Apple Charlotte Cake</t>
+    <t>Куриный с фрикадельками и рисом</t>
+  </si>
+  <si>
+    <t>куриный фарш, картофель, лук, морковь, чеснок, специи, вермишель</t>
   </si>
   <si>
     <t>Bliny</t>
   </si>
   <si>
+    <t>baked-wheat-tarts-tomato-mozzarella.jpg</t>
+  </si>
+  <si>
+    <t>with Vermicelli</t>
+  </si>
+  <si>
+    <t>Gastro Boxes</t>
+  </si>
+  <si>
     <t>bliny.jpd</t>
   </si>
   <si>
-    <t>apples, sugar, flour, vanilla, eggs</t>
-  </si>
-  <si>
-    <t>Beef and Mushrooms Salad</t>
-  </si>
-  <si>
-    <t>sharlotka.jpg</t>
+    <t>Bruschetta with Beef</t>
+  </si>
+  <si>
+    <t>ground chicken, potatoes, onion, carrots, garlic, seasonings, rice</t>
+  </si>
+  <si>
+    <t>Eclairs with Seafood Dressing</t>
   </si>
   <si>
     <t>Bliny with cottage cheese</t>
   </si>
   <si>
-    <t>Шарлотка</t>
-  </si>
-  <si>
-    <t>яблоки, сахар, мука, ванилин, яйца</t>
-  </si>
-  <si>
-    <t>chicken, apples, celey, mustard dressing</t>
-  </si>
-  <si>
-    <t>beef-mushrooms-salad.jpg</t>
+    <t>Minimum order of one type bruschetta - 10 pieces</t>
+  </si>
+  <si>
+    <t>bruschetta.jpg</t>
+  </si>
+  <si>
+    <t>Куриный с фрикадельками и вермишелью</t>
   </si>
   <si>
     <t>cottage-cheese-bliny.jpg</t>
   </si>
   <si>
-    <t>Crepes</t>
-  </si>
-  <si>
-    <t>crepes</t>
+    <t>куриный фарш, картофель, лук, морковь, чеснок, специи, рис</t>
+  </si>
+  <si>
+    <t>eclairs-seafood.jpg</t>
+  </si>
+  <si>
+    <t>Bruschetta with Salmon</t>
+  </si>
+  <si>
+    <t>Sauerkraut Cabbage Soup</t>
   </si>
   <si>
     <t>Bliny with apple</t>
   </si>
   <si>
-    <t>Apple Salad</t>
-  </si>
-  <si>
-    <t>eggs, milk, flour, butter, sugar, salt, vanilla</t>
-  </si>
-  <si>
-    <t>crepes.jpg</t>
+    <t>Chicken Kebabs with Vegetables</t>
+  </si>
+  <si>
+    <t>sauerkraut, potatoes, carrots, onion, seasonings</t>
   </si>
   <si>
     <t>apple-bliny.jpg</t>
   </si>
   <si>
-    <t>apple-salad.jpg</t>
-  </si>
-  <si>
-    <t>Блины</t>
+    <t>sauerkraut-cabbage-soup.jpg</t>
+  </si>
+  <si>
+    <t>Bruschetta with Shrimp</t>
   </si>
   <si>
     <t>Mini syrniki</t>
   </si>
   <si>
-    <t>яйца, молоко, мука, масло, сахар, соль, ванилин</t>
-  </si>
-  <si>
-    <t>mini-syrniki.jpg</t>
-  </si>
-  <si>
-    <t>Mexican Tortilla with Cream Cheese, Salmon and Herbs</t>
-  </si>
-  <si>
-    <t>with Cottage Cheese</t>
+    <t>Щи из квашенной капусты</t>
+  </si>
+  <si>
+    <t>chicken-kebabs-vegetables.jpg</t>
+  </si>
+  <si>
+    <t>квашенная капуста, картофель, морковь, лук, специи</t>
+  </si>
+  <si>
+    <t>Bean Soup with Beef</t>
+  </si>
+  <si>
+    <t>Pork Kebabs</t>
   </si>
   <si>
     <t>Baked cheese and chicken tartlets</t>
   </si>
   <si>
-    <t>farmer's cheese, eggs, milk, flour, butter, sugar, salt, vanilla</t>
-  </si>
-  <si>
-    <t>crepes-cottage-cheese.jpg</t>
+    <t>Bruschetta with Mushrooms</t>
+  </si>
+  <si>
+    <t>beef, canned beans, potatoes, onion, garlic, carrots, seasonings</t>
+  </si>
+  <si>
+    <t>bean-soup.jpg</t>
   </si>
   <si>
     <t>cheese-chicken-tartlets.jpg</t>
   </si>
   <si>
-    <t>Блины с творогом</t>
-  </si>
-  <si>
-    <t>творог, яйца, молоко, мука, масло, сахар, соль, ванилин</t>
-  </si>
-  <si>
-    <t>mexican-tortilla-salmon.jpg</t>
+    <t>Фасолевый с говядиной</t>
+  </si>
+  <si>
+    <t>pork-kebabs.jpg</t>
+  </si>
+  <si>
+    <t>говядина, фасоль консервированная, картофель, лук, чеснок, морковь, специи</t>
+  </si>
+  <si>
+    <t>Bruschetta with Sun-Dried Tomatoes</t>
   </si>
   <si>
     <t>Mini chicken and zucchini skewers</t>
   </si>
   <si>
-    <t>with Chicken</t>
-  </si>
-  <si>
-    <t>Mini Syrniki with a Pattern</t>
+    <t>Salmon and Vegetable kebabs</t>
   </si>
   <si>
     <t>mini-chicken-zucchini-skewers.jpg</t>
   </si>
   <si>
-    <t>chicken, eggs, milk, flour, butter, sugar, salt, broth, seasonings</t>
-  </si>
-  <si>
-    <t>Блины с курицей</t>
-  </si>
-  <si>
-    <t>курица, яйца, молоко, мука, масло, сахар, соль, бульон, специи</t>
-  </si>
-  <si>
-    <t>Blinchiki with Spinach, Salmon, and Cream Cheese</t>
-  </si>
-  <si>
-    <t>with Beef</t>
-  </si>
-  <si>
-    <t>blinchiki-salmon-spinach-creamcheese.jpg</t>
-  </si>
-  <si>
-    <t>beef, eggs, milk, flour, butter, sugar, salt, broth, seasonings</t>
-  </si>
-  <si>
-    <t>Блины с говядиной</t>
-  </si>
-  <si>
-    <t>говядина, яйца, молоко, мука, масло, сахар, соль, бульон, специи</t>
-  </si>
-  <si>
-    <t>Binchiki with Salmon, Cream Cheese and Greens</t>
-  </si>
-  <si>
-    <t>with Smoked Salmon</t>
-  </si>
-  <si>
-    <t>blinchiki-salmon-creamcheese.jpg</t>
-  </si>
-  <si>
-    <t>cream cheese, salmon, fresh herbs, flour, milk, eggs, salt, sugar</t>
-  </si>
-  <si>
-    <t>Blinchiki with Mushrooms</t>
-  </si>
-  <si>
-    <t>Блины с лососем</t>
-  </si>
-  <si>
-    <t>крем-чиз, лосось, зелень, мука, молоко, яйца, соль, сахар</t>
-  </si>
-  <si>
-    <t>blinchiki-mushrooms.jpg</t>
-  </si>
-  <si>
-    <t>with Apples</t>
-  </si>
-  <si>
-    <t>Blinchiki with Apple</t>
-  </si>
-  <si>
-    <t>apples, eggs, milk, flour, butter, sugar, salt, vanilla</t>
-  </si>
-  <si>
-    <t>blinchiki-apple.jpg</t>
-  </si>
-  <si>
-    <t>Блины с яблоками</t>
-  </si>
-  <si>
-    <t>яблоки, яйца, молоко, мука, масло, сахар, соль, ванилин</t>
-  </si>
-  <si>
-    <t>Mushroom Julienne in Tartlets</t>
-  </si>
-  <si>
-    <t>with Mushrooms</t>
-  </si>
-  <si>
-    <t>mushrooms, eggs, milk, flour, butter, sugar, salt, sour cream</t>
-  </si>
-  <si>
-    <t>mushroom-julienne-tartlets.jpg</t>
-  </si>
-  <si>
-    <t>Блины с грибами</t>
-  </si>
-  <si>
-    <t>грибы, яйца, молоко, мука, масло, сахар, соль, сметана</t>
-  </si>
-  <si>
-    <t>Pancake Bags with Julienne</t>
-  </si>
-  <si>
-    <t>Borscht</t>
-  </si>
-  <si>
-    <t>borscht</t>
-  </si>
-  <si>
-    <t>Chicken</t>
-  </si>
-  <si>
-    <t>pancake-julienne.jpg</t>
-  </si>
-  <si>
-    <t>liter</t>
-  </si>
-  <si>
-    <t>Gastro Boxes</t>
-  </si>
-  <si>
-    <t>Bruschetta with Beef</t>
-  </si>
-  <si>
-    <t>chicken, beets, potatoes, onion, carrots, garlic, seasonings, sugar, vinegar</t>
-  </si>
-  <si>
-    <t>borscht.jpg</t>
-  </si>
-  <si>
-    <t>Супы</t>
-  </si>
-  <si>
-    <t>Борщ с курицей</t>
-  </si>
-  <si>
-    <t>Minimum order of one type bruschetta - 10 pieces</t>
-  </si>
-  <si>
-    <t>Profittroles with Ice Cream Fruit</t>
-  </si>
-  <si>
-    <t>курица, свекла, картофель, лук, морковь, чеснок, специи, сахар, уксус</t>
-  </si>
-  <si>
-    <t>bruschetta.jpg</t>
-  </si>
-  <si>
-    <t>Beef</t>
-  </si>
-  <si>
-    <t>profittroles-icecream-fruit.jpg</t>
-  </si>
-  <si>
-    <t>Bruschetta with Salmon</t>
-  </si>
-  <si>
-    <t>beef, beets, potatoes, onion, carrots, garlic, seasonings, sugar, vinegar</t>
-  </si>
-  <si>
-    <t>Baked Wheat Tarts with Tomato and Mozzarella Cheese</t>
-  </si>
-  <si>
-    <t>Борщ с говядиной</t>
-  </si>
-  <si>
-    <t>говядина, свекла, картофель, лук, морковь, чеснок, специи, сахар, уксус</t>
-  </si>
-  <si>
-    <t>Bruschetta with Shrimp</t>
-  </si>
-  <si>
-    <t>baked-wheat-tarts-tomato-mozzarella.jpg</t>
-  </si>
-  <si>
-    <t>Sorrel Soup with Beef</t>
-  </si>
-  <si>
-    <t>Eclairs with Seafood Dressing</t>
-  </si>
-  <si>
-    <t>sorrel, beef, potatoes, eggs, onion, carrots, garlic, seasonings, sugar</t>
-  </si>
-  <si>
-    <t>sorrel-soup.jpg</t>
-  </si>
-  <si>
-    <t>Bruschetta with Mushrooms</t>
-  </si>
-  <si>
-    <t>eclairs-seafood.jpg</t>
-  </si>
-  <si>
-    <t>Щавелевый с говядиной</t>
-  </si>
-  <si>
-    <t>щавель, говядина, картофель, яйца, лук, морковь, чеснок, специи, сахар</t>
-  </si>
-  <si>
-    <t>Chicken Kebabs with Vegetables</t>
-  </si>
-  <si>
-    <t>Chicken Meatball Soup</t>
-  </si>
-  <si>
-    <t>Bruschetta with Sun-Dried Tomatoes</t>
-  </si>
-  <si>
-    <t>with Rice</t>
-  </si>
-  <si>
-    <t>chicken-kebabs-vegetables.jpg</t>
-  </si>
-  <si>
-    <t>ground chicken, potatoes, onion, carrots, garlic, seasonings, vermicelli</t>
-  </si>
-  <si>
-    <t>chicken-meatball-soup.jpg</t>
-  </si>
-  <si>
-    <t>Pork Kebabs</t>
-  </si>
-  <si>
-    <t>Куриный с фрикадельками и рисом</t>
-  </si>
-  <si>
-    <t>куриный фарш, картофель, лук, морковь, чеснок, специи, вермишель</t>
-  </si>
-  <si>
     <t>Bruschetta with Sprats</t>
   </si>
   <si>
-    <t>pork-kebabs.jpg</t>
-  </si>
-  <si>
-    <t>with Vermicelli</t>
-  </si>
-  <si>
-    <t>Salmon and Vegetable kebabs</t>
-  </si>
-  <si>
-    <t>ground chicken, potatoes, onion, carrots, garlic, seasonings, rice</t>
+    <t>salmon-vegetable-kebabs.jpg</t>
+  </si>
+  <si>
+    <t>Solyanka</t>
+  </si>
+  <si>
+    <t>Beef Kebabs with Mushrooms</t>
   </si>
   <si>
     <t>Bruschetta with Fruits and Berries</t>
   </si>
   <si>
-    <t>salmon-vegetable-kebabs.jpg</t>
-  </si>
-  <si>
-    <t>Куриный с фрикадельками и вермишелью</t>
-  </si>
-  <si>
-    <t>куриный фарш, картофель, лук, морковь, чеснок, специи, рис</t>
-  </si>
-  <si>
-    <t>Sauerkraut Cabbage Soup</t>
-  </si>
-  <si>
-    <t>Beef Kebabs with Mushrooms</t>
+    <t>Hearty smoked meat soup</t>
+  </si>
+  <si>
+    <t>assorted smoked meats, onions sautéed with tomatoes, pickles simmered in tomato paste, potatoes, seasonings, olives, sugar, lemon</t>
+  </si>
+  <si>
+    <t>solyanka.jpg</t>
+  </si>
+  <si>
+    <t>beef-kebabs-mushrooms.jpg</t>
+  </si>
+  <si>
+    <t>Солянка</t>
+  </si>
+  <si>
+    <t>мясные колбасы, лук жаренный с томатами, маринованный огурец томленный в томатной пасте, картофель, специи, маслины, сахар, лимон</t>
   </si>
   <si>
     <t>Bruschetta 2 boxes</t>
   </si>
   <si>
-    <t>sauerkraut, potatoes, carrots, onion, seasonings</t>
-  </si>
-  <si>
-    <t>sauerkraut-cabbage-soup.jpg</t>
-  </si>
-  <si>
-    <t>beef-kebabs-mushrooms.jpg</t>
-  </si>
-  <si>
-    <t>Щи из квашенной капусты</t>
-  </si>
-  <si>
-    <t>квашенная капуста, картофель, морковь, лук, специи</t>
+    <t>Jelly in Plates with Chicken</t>
+  </si>
+  <si>
+    <t>Beef Rassolnik</t>
+  </si>
+  <si>
+    <t>jelly-chicken--plates.jpg</t>
+  </si>
+  <si>
+    <t>Traditional pickle soup with beef</t>
+  </si>
+  <si>
+    <t>beef, pearl barley, pickles, potatoes, onion, garlic, carrots, seasonings, sugar</t>
+  </si>
+  <si>
+    <t>rassolnik.jpg</t>
   </si>
   <si>
     <t>Bruschetta</t>
   </si>
   <si>
-    <t>Bean Soup with Beef</t>
-  </si>
-  <si>
-    <t>Jelly in Plates with Chicken</t>
-  </si>
-  <si>
-    <t>beef, canned beans, potatoes, onion, garlic, carrots, seasonings</t>
+    <t>Jelly in Plates with Beef</t>
+  </si>
+  <si>
+    <t>Рассольник с говядиной</t>
+  </si>
+  <si>
+    <t>говядина, перловая крупа, огурец маринованный, картофель, лук, чеснок, морковь, специи, сахар</t>
   </si>
   <si>
     <t>Грибы жареные</t>
   </si>
   <si>
-    <t>bean-soup.jpg</t>
-  </si>
-  <si>
-    <t>jelly-chicken--plates.jpg</t>
-  </si>
-  <si>
-    <t>Фасолевый с говядиной</t>
-  </si>
-  <si>
-    <t>говядина, фасоль консервированная, картофель, лук, чеснок, морковь, специи</t>
-  </si>
-  <si>
-    <t>Solyanka</t>
-  </si>
-  <si>
-    <t>Jelly in Plates with Beef</t>
+    <t>Split Pea Soup with Smoked Sausage</t>
+  </si>
+  <si>
+    <t>jelly-beef-plates.jpg</t>
+  </si>
+  <si>
+    <t>split peas, smoked sausage, potatoes, onion, garlic, carrots, seasonings</t>
+  </si>
+  <si>
+    <t>split-pea-soup.jpg</t>
+  </si>
+  <si>
+    <t>Jelly Tongue in Cups</t>
   </si>
   <si>
     <t>Селедка</t>
   </si>
   <si>
-    <t>Hearty smoked meat soup</t>
-  </si>
-  <si>
-    <t>jelly-beef-plates.jpg</t>
-  </si>
-  <si>
-    <t>assorted smoked meats, onions sautéed with tomatoes, pickles simmered in tomato paste, potatoes, seasonings, olives, sugar, lemon</t>
-  </si>
-  <si>
-    <t>solyanka.jpg</t>
-  </si>
-  <si>
-    <t>Солянка</t>
-  </si>
-  <si>
-    <t>Jelly Tongue in Cups</t>
-  </si>
-  <si>
-    <t>мясные колбасы, лук жаренный с томатами, маринованный огурец томленный в томатной пасте, картофель, специи, маслины, сахар, лимон</t>
+    <t>Гороховый с копчеными колбасками</t>
+  </si>
+  <si>
+    <t>горох, колбаски копченые, картофель, лук, чеснок, морковь, специи</t>
+  </si>
+  <si>
+    <t>jelly-tongue-cups.jpg</t>
+  </si>
+  <si>
+    <t>Mushroom Soup with Chicken</t>
   </si>
   <si>
     <t>Запеченные с грушей и сыром бри</t>
   </si>
   <si>
-    <t>Beef Rassolnik</t>
-  </si>
-  <si>
-    <t>Traditional pickle soup with beef</t>
-  </si>
-  <si>
-    <t>jelly-tongue-cups.jpg</t>
-  </si>
-  <si>
-    <t>beef, pearl barley, pickles, potatoes, onion, garlic, carrots, seasonings, sugar</t>
-  </si>
-  <si>
-    <t>rassolnik.jpg</t>
+    <t>button mushrooms, chicken, potatoes, onion, garlic, carrots, seasonings</t>
+  </si>
+  <si>
+    <t>Baked Mushrooms with Minced Meat or Vegetables</t>
+  </si>
+  <si>
+    <t>mushroom-soup.jpg</t>
+  </si>
+  <si>
+    <t>Грибной с курицей</t>
+  </si>
+  <si>
+    <t>baked-mushrooms-minced-meat-vegetables.jpg</t>
+  </si>
+  <si>
+    <t>шампиньоны, курица, картофель, лук, чеснок, морковь, специи</t>
   </si>
   <si>
     <t>С сыром дор блю и фруктами</t>
   </si>
   <si>
-    <t>Рассольник с говядиной</t>
-  </si>
-  <si>
-    <t>Baked Mushrooms with Minced Meat or Vegetables</t>
-  </si>
-  <si>
-    <t>говядина, перловая крупа, огурец маринованный, картофель, лук, чеснок, морковь, специи, сахар</t>
-  </si>
-  <si>
-    <t>Split Pea Soup with Smoked Sausage</t>
-  </si>
-  <si>
-    <t>baked-mushrooms-minced-meat-vegetables.jpg</t>
+    <t>White Fish Soup</t>
+  </si>
+  <si>
+    <t>Jelly Beef in Cups (from 10 psc)</t>
+  </si>
+  <si>
+    <t>white fish, potatoes, onion, carrots, seasonings</t>
+  </si>
+  <si>
+    <t>white-fish-soup.jpg</t>
   </si>
   <si>
     <t>С томатом, луком и авокадо</t>
   </si>
   <si>
-    <t>split peas, smoked sausage, potatoes, onion, garlic, carrots, seasonings</t>
-  </si>
-  <si>
-    <t>split-pea-soup.jpg</t>
-  </si>
-  <si>
-    <t>Jelly Beef in Cups (from 10 psc)</t>
-  </si>
-  <si>
-    <t>Гороховый с копчеными колбасками</t>
-  </si>
-  <si>
-    <t>горох, колбаски копченые, картофель, лук, чеснок, морковь, специи</t>
-  </si>
-  <si>
-    <t>Mushroom Soup with Chicken</t>
-  </si>
-  <si>
     <t>jelly-beef-cups.jpg</t>
   </si>
   <si>
-    <t>button mushrooms, chicken, potatoes, onion, garlic, carrots, seasonings</t>
-  </si>
-  <si>
-    <t>mushroom-soup.jpg</t>
+    <t>Уха из белой рыбы</t>
+  </si>
+  <si>
+    <t>белая рыба,картофель. лук, морковь, специи</t>
+  </si>
+  <si>
+    <t>Kholodnik (Cold Beet Soup)</t>
   </si>
   <si>
     <t>Canapes in Cups (you can choose any composition of canapes: vegetables, fish, sausage, olives, cheese, etc.)</t>
   </si>
   <si>
-    <t>Грибной с курицей</t>
-  </si>
-  <si>
-    <t>шампиньоны, курица, картофель, лук, чеснок, морковь, специи</t>
+    <t>Chilled beet soup</t>
+  </si>
+  <si>
+    <t>kefir, beets, water, eggs, cucumber, green onions, dill, citric acid, sugar</t>
+  </si>
+  <si>
+    <t>kholodnik.jpg</t>
   </si>
   <si>
     <t>canapes-cups-main.jpg</t>
-  </si>
-  <si>
-    <t>White Fish Soup</t>
-  </si>
-  <si>
-    <t>white fish, potatoes, onion, carrots, seasonings</t>
-  </si>
-  <si>
-    <t>white-fish-soup.jpg</t>
-  </si>
-  <si>
-    <t>Уха из белой рыбы</t>
-  </si>
-  <si>
-    <t>белая рыба,картофель. лук, морковь, специи</t>
-  </si>
-  <si>
-    <t>Kholodnik (Cold Beet Soup)</t>
-  </si>
-  <si>
-    <t>Chilled beet soup</t>
-  </si>
-  <si>
-    <t>kefir, beets, water, eggs, cucumber, green onions, dill, citric acid, sugar</t>
-  </si>
-  <si>
-    <t>kholodnik.jpg</t>
   </si>
   <si>
     <t>Холодник</t>
@@ -2222,10 +2222,10 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C2" s="1">
         <v>1.0</v>
@@ -2233,10 +2233,10 @@
     </row>
     <row r="3">
       <c r="A3" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="C3" s="1">
         <v>2.0</v>
@@ -2244,10 +2244,10 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="C4" s="1">
         <v>3.0</v>
@@ -2255,10 +2255,10 @@
     </row>
     <row r="5">
       <c r="A5" s="1" t="s">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="C5" s="1">
         <v>4.0</v>
@@ -2286,7 +2286,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>2</v>
@@ -2294,10 +2294,10 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C2" s="1">
         <v>1.0</v>
@@ -2305,10 +2305,10 @@
     </row>
     <row r="3">
       <c r="A3" s="1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C3" s="1">
         <v>2.0</v>
@@ -2316,10 +2316,10 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="C4" s="1">
         <v>3.0</v>
@@ -2327,10 +2327,10 @@
     </row>
     <row r="5">
       <c r="A5" s="1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="C5" s="1">
         <v>4.0</v>
@@ -2338,10 +2338,10 @@
     </row>
     <row r="6">
       <c r="A6" s="1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="C6" s="1">
         <v>5.0</v>
@@ -2349,10 +2349,10 @@
     </row>
     <row r="7">
       <c r="A7" s="1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="C7" s="1">
         <v>6.0</v>
@@ -2360,10 +2360,10 @@
     </row>
     <row r="8">
       <c r="A8" s="1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="C8" s="1">
         <v>7.0</v>
@@ -2371,10 +2371,10 @@
     </row>
     <row r="9">
       <c r="A9" s="1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="C9" s="1">
         <v>8.0</v>
@@ -2382,10 +2382,10 @@
     </row>
     <row r="10">
       <c r="A10" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="C10" s="1">
         <v>1.0</v>
@@ -2393,10 +2393,10 @@
     </row>
     <row r="11">
       <c r="A11" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="C11" s="1">
         <v>2.0</v>
@@ -2404,10 +2404,10 @@
     </row>
     <row r="12">
       <c r="A12" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="C12" s="1">
         <v>3.0</v>
@@ -2415,10 +2415,10 @@
     </row>
     <row r="13">
       <c r="A13" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="C13" s="1">
         <v>4.0</v>
@@ -2426,10 +2426,10 @@
     </row>
     <row r="14">
       <c r="A14" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>31</v>
+        <v>43</v>
       </c>
       <c r="C14" s="1">
         <v>5.0</v>
@@ -2437,10 +2437,10 @@
     </row>
     <row r="15">
       <c r="A15" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="C15" s="1">
         <v>6.0</v>
@@ -2448,10 +2448,10 @@
     </row>
     <row r="16">
       <c r="A16" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="C16" s="1">
         <v>7.0</v>
@@ -2459,10 +2459,10 @@
     </row>
     <row r="17">
       <c r="A17" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="C17" s="1">
         <v>8.0</v>
@@ -2470,12 +2470,12 @@
     </row>
     <row r="18">
       <c r="A18" s="1" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="s">
-        <v>9</v>
+        <v>18</v>
       </c>
     </row>
   </sheetData>
@@ -2506,90 +2506,90 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="E1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="I1" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="F1" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="H1" s="1" t="s">
+      <c r="J1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="I1" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="J1" s="1" t="s">
+      <c r="L1" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="N1" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="L1" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="M1" s="1" t="s">
+      <c r="P1" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q1" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="R1" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="S1" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="P1" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="Q1" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="R1" s="1" t="s">
+      <c r="T1" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="V1" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="W1" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="X1" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="U1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="V1" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="W1" s="1" t="s">
+      <c r="Y1" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="X1" s="1" t="s">
+      <c r="Z1" s="1" t="s">
         <v>45</v>
-      </c>
-      <c r="Y1" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="Z1" s="1" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D2" s="1" t="b">
         <v>0</v>
@@ -2599,22 +2599,22 @@
         <v>20.0</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="I2" s="1">
         <v>2.0</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="K2" s="1">
         <v>70.0</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="P2" s="1" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="Q2" s="1">
         <v>1.0</v>
@@ -2631,13 +2631,13 @@
     </row>
     <row r="3">
       <c r="A3" s="1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="D3" s="1" t="b">
         <v>0</v>
@@ -2647,22 +2647,22 @@
         <v>20.0</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="I3" s="1">
         <v>2.0</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="K3" s="1">
         <v>70.0</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="P3" s="1" t="s">
-        <v>54</v>
+        <v>64</v>
       </c>
       <c r="Q3" s="1">
         <v>2.0</v>
@@ -2679,13 +2679,13 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="D4" s="1" t="b">
         <v>0</v>
@@ -2695,22 +2695,22 @@
         <v>20.0</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="I4" s="1">
         <v>2.0</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="K4" s="1">
         <v>70.0</v>
       </c>
       <c r="L4" s="1" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="P4" s="1" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="Q4" s="1">
         <v>3.0</v>
@@ -2727,13 +2727,13 @@
     </row>
     <row r="5">
       <c r="A5" s="1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="D5" s="1" t="b">
         <v>0</v>
@@ -2743,22 +2743,22 @@
         <v>20.0</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="I5" s="1">
         <v>2.0</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="K5" s="1">
         <v>70.0</v>
       </c>
       <c r="L5" s="1" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="P5" s="1" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="Q5" s="1">
         <v>4.0</v>
@@ -2775,37 +2775,37 @@
     </row>
     <row r="6">
       <c r="A6" s="1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="D6" s="1" t="b">
         <v>0</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="I6" s="1">
         <v>4.0</v>
       </c>
       <c r="J6" s="1" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="K6" s="1">
         <v>60.0</v>
       </c>
       <c r="L6" s="1" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="N6" s="2" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="P6" s="1" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="Q6" s="1">
         <v>1.0</v>
@@ -2822,10 +2822,10 @@
     </row>
     <row r="7">
       <c r="A7" s="1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>80</v>
@@ -2834,22 +2834,22 @@
         <v>0</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="I7" s="1">
         <v>4.0</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="K7" s="1">
         <v>70.0</v>
       </c>
       <c r="L7" s="1" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="N7" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="P7" s="1" t="s">
         <v>84</v>
@@ -2869,37 +2869,37 @@
     </row>
     <row r="8">
       <c r="A8" s="1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="D8" s="1" t="b">
         <v>0</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="I8" s="1">
         <v>4.0</v>
       </c>
       <c r="J8" s="1" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="K8" s="1">
         <v>60.0</v>
       </c>
       <c r="L8" s="1" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="N8" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="P8" s="1" t="s">
         <v>90</v>
-      </c>
-      <c r="P8" s="1" t="s">
-        <v>92</v>
       </c>
       <c r="Q8" s="1">
         <v>3.0</v>
@@ -2916,37 +2916,37 @@
     </row>
     <row r="9">
       <c r="A9" s="1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="D9" s="1" t="b">
         <v>0</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="I9" s="1">
         <v>4.0</v>
       </c>
       <c r="J9" s="1" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="K9" s="1">
         <v>60.0</v>
       </c>
       <c r="L9" s="1" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="N9" s="2" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="P9" s="1" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="Q9" s="1">
         <v>4.0</v>
@@ -2963,37 +2963,37 @@
     </row>
     <row r="10">
       <c r="A10" s="1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="D10" s="1" t="b">
         <v>0</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="I10" s="1">
         <v>4.0</v>
       </c>
       <c r="J10" s="1" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="K10" s="1">
         <v>60.0</v>
       </c>
       <c r="L10" s="1" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="N10" s="2" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="P10" s="1" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="Q10" s="1">
         <v>5.0</v>
@@ -3010,37 +3010,37 @@
     </row>
     <row r="11">
       <c r="A11" s="1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="D11" s="1" t="b">
         <v>0</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="I11" s="1">
         <v>4.0</v>
       </c>
       <c r="J11" s="1" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="K11" s="1">
         <v>60.0</v>
       </c>
       <c r="L11" s="1" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="N11" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="P11" s="1" t="s">
         <v>111</v>
-      </c>
-      <c r="P11" s="1" t="s">
-        <v>121</v>
       </c>
       <c r="Q11" s="1">
         <v>6.0</v>
@@ -3057,13 +3057,13 @@
     </row>
     <row r="12">
       <c r="A12" s="1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>126</v>
+        <v>114</v>
       </c>
       <c r="D12" s="1" t="b">
         <v>0</v>
@@ -3073,22 +3073,22 @@
         <v>20.0</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="I12" s="1">
         <v>3.0</v>
       </c>
       <c r="J12" s="1" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="K12" s="1">
         <v>60.0</v>
       </c>
       <c r="L12" s="1" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="P12" s="1" t="s">
-        <v>134</v>
+        <v>117</v>
       </c>
       <c r="Q12" s="1">
         <v>1.0</v>
@@ -3105,13 +3105,13 @@
     </row>
     <row r="13">
       <c r="A13" s="1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>137</v>
+        <v>120</v>
       </c>
       <c r="D13" s="1" t="b">
         <v>0</v>
@@ -3121,22 +3121,22 @@
         <v>20.0</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="I13" s="1">
         <v>3.0</v>
       </c>
       <c r="J13" s="1" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="K13" s="1">
         <v>70.0</v>
       </c>
       <c r="L13" s="1" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="P13" s="1" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="Q13" s="1">
         <v>2.0</v>
@@ -3153,13 +3153,13 @@
     </row>
     <row r="14">
       <c r="A14" s="1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>142</v>
+        <v>124</v>
       </c>
       <c r="D14" s="1" t="b">
         <v>0</v>
@@ -3169,22 +3169,22 @@
         <v>20.0</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="I14" s="1">
         <v>3.0</v>
       </c>
       <c r="J14" s="1" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="K14" s="1">
         <v>60.0</v>
       </c>
       <c r="L14" s="1" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="P14" s="1" t="s">
-        <v>144</v>
+        <v>128</v>
       </c>
       <c r="Q14" s="1">
         <v>3.0</v>
@@ -3201,13 +3201,13 @@
     </row>
     <row r="15">
       <c r="A15" s="1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>148</v>
+        <v>130</v>
       </c>
       <c r="D15" s="1" t="b">
         <v>0</v>
@@ -3217,22 +3217,22 @@
         <v>20.0</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="I15" s="1">
         <v>3.0</v>
       </c>
       <c r="J15" s="1" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="K15" s="1">
         <v>70.0</v>
       </c>
       <c r="L15" s="1" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="P15" s="1" t="s">
-        <v>150</v>
+        <v>133</v>
       </c>
       <c r="Q15" s="1">
         <v>4.0</v>
@@ -3249,13 +3249,13 @@
     </row>
     <row r="16">
       <c r="A16" s="1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>152</v>
+        <v>136</v>
       </c>
       <c r="D16" s="1" t="b">
         <v>0</v>
@@ -3265,22 +3265,22 @@
         <v>20.0</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="I16" s="1">
         <v>3.0</v>
       </c>
       <c r="J16" s="1" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="K16" s="1">
         <v>60.0</v>
       </c>
       <c r="L16" s="1" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="P16" s="1" t="s">
-        <v>155</v>
+        <v>139</v>
       </c>
       <c r="Q16" s="1">
         <v>5.0</v>
@@ -3297,13 +3297,13 @@
     </row>
     <row r="17">
       <c r="A17" s="1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>157</v>
+        <v>142</v>
       </c>
       <c r="D17" s="1" t="b">
         <v>0</v>
@@ -3313,22 +3313,22 @@
         <v>20.0</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="I17" s="1">
         <v>3.0</v>
       </c>
       <c r="J17" s="1" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="K17" s="1">
         <v>60.0</v>
       </c>
       <c r="L17" s="1" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="P17" s="1" t="s">
-        <v>159</v>
+        <v>151</v>
       </c>
       <c r="Q17" s="1">
         <v>6.0</v>
@@ -3345,13 +3345,13 @@
     </row>
     <row r="18">
       <c r="A18" s="1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="D18" s="1" t="b">
         <v>0</v>
@@ -3361,19 +3361,19 @@
         <v>15.0</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="J18" s="1" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="K18" s="1">
         <v>80.0</v>
       </c>
       <c r="L18" s="1" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="P18" s="1" t="s">
-        <v>165</v>
+        <v>158</v>
       </c>
       <c r="Q18" s="1">
         <v>1.0</v>
@@ -3390,13 +3390,13 @@
     </row>
     <row r="19">
       <c r="A19" s="1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="D19" s="1" t="b">
         <v>0</v>
@@ -3406,19 +3406,19 @@
         <v>15.0</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="J19" s="1" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="K19" s="1">
         <v>80.0</v>
       </c>
       <c r="L19" s="1" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="P19" s="1" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="Q19" s="1">
         <v>2.0</v>
@@ -3435,13 +3435,13 @@
     </row>
     <row r="20">
       <c r="A20" s="1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>181</v>
+        <v>173</v>
       </c>
       <c r="D20" s="1" t="b">
         <v>0</v>
@@ -3451,19 +3451,19 @@
         <v>20.0</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="J20" s="1" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="K20" s="1">
         <v>100.0</v>
       </c>
       <c r="L20" s="1" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="P20" s="1" t="s">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="Q20" s="1">
         <v>3.0</v>
@@ -3480,13 +3480,13 @@
     </row>
     <row r="21">
       <c r="A21" s="1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>188</v>
+        <v>182</v>
       </c>
       <c r="D21" s="1" t="b">
         <v>0</v>
@@ -3496,19 +3496,19 @@
         <v>15.0</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="J21" s="1" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="K21" s="1">
         <v>80.0</v>
       </c>
       <c r="L21" s="1" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="P21" s="1" t="s">
-        <v>192</v>
+        <v>187</v>
       </c>
       <c r="Q21" s="1">
         <v>4.0</v>
@@ -3525,13 +3525,13 @@
     </row>
     <row r="22">
       <c r="A22" s="1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="D22" s="1" t="b">
         <v>0</v>
@@ -3541,19 +3541,19 @@
         <v>20.0</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="J22" s="1" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="K22" s="1">
         <v>100.0</v>
       </c>
       <c r="L22" s="1" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="P22" s="1" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="Q22" s="1">
         <v>5.0</v>
@@ -3570,13 +3570,13 @@
     </row>
     <row r="23">
       <c r="A23" s="1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="D23" s="1" t="b">
         <v>0</v>
@@ -3586,19 +3586,19 @@
         <v>8.0</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="J23" s="1" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="K23" s="1">
         <v>80.0</v>
       </c>
       <c r="L23" s="1" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="P23" s="1" t="s">
-        <v>205</v>
+        <v>211</v>
       </c>
       <c r="Q23" s="1">
         <v>1.0</v>
@@ -3615,13 +3615,13 @@
     </row>
     <row r="24">
       <c r="A24" s="1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="D24" s="1" t="b">
         <v>0</v>
@@ -3631,19 +3631,19 @@
         <v>8.0</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="J24" s="1" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="K24" s="1">
         <v>80.0</v>
       </c>
       <c r="L24" s="1" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="P24" s="1" t="s">
-        <v>212</v>
+        <v>221</v>
       </c>
       <c r="Q24" s="1">
         <v>2.0</v>
@@ -3660,13 +3660,13 @@
     </row>
     <row r="25">
       <c r="A25" s="1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>214</v>
+        <v>225</v>
       </c>
       <c r="D25" s="1" t="b">
         <v>0</v>
@@ -3676,19 +3676,19 @@
         <v>6.0</v>
       </c>
       <c r="H25" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="J25" s="1" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="K25" s="1">
         <v>80.0</v>
       </c>
       <c r="L25" s="1" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="P25" s="1" t="s">
-        <v>217</v>
+        <v>228</v>
       </c>
       <c r="Q25" s="1">
         <v>3.0</v>
@@ -3705,13 +3705,13 @@
     </row>
     <row r="26">
       <c r="A26" s="1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>221</v>
+        <v>230</v>
       </c>
       <c r="D26" s="1" t="b">
         <v>0</v>
@@ -3721,19 +3721,19 @@
         <v>8.0</v>
       </c>
       <c r="H26" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="J26" s="1" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="K26" s="1">
         <v>80.0</v>
       </c>
       <c r="L26" s="1" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="P26" s="1" t="s">
-        <v>225</v>
+        <v>235</v>
       </c>
       <c r="Q26" s="1">
         <v>4.0</v>
@@ -3750,34 +3750,34 @@
     </row>
     <row r="27">
       <c r="A27" s="1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>230</v>
+        <v>239</v>
       </c>
       <c r="D27" s="1" t="b">
         <v>0</v>
       </c>
       <c r="H27" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="I27" s="1">
         <v>2.0</v>
       </c>
       <c r="J27" s="1" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="K27" s="1">
         <v>50.0</v>
       </c>
       <c r="L27" s="1" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="P27" s="1" t="s">
-        <v>234</v>
+        <v>241</v>
       </c>
       <c r="Q27" s="1">
         <v>1.0</v>
@@ -3794,34 +3794,34 @@
     </row>
     <row r="28">
       <c r="A28" s="1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>238</v>
+        <v>246</v>
       </c>
       <c r="D28" s="1" t="b">
         <v>0</v>
       </c>
       <c r="H28" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="I28" s="1">
         <v>2.0</v>
       </c>
       <c r="J28" s="1" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="K28" s="1">
         <v>50.0</v>
       </c>
       <c r="L28" s="1" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="P28" s="1" t="s">
-        <v>241</v>
+        <v>251</v>
       </c>
       <c r="Q28" s="1">
         <v>2.0</v>
@@ -3838,13 +3838,13 @@
     </row>
     <row r="29">
       <c r="A29" s="1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>245</v>
+        <v>254</v>
       </c>
       <c r="D29" s="1" t="b">
         <v>0</v>
@@ -3854,19 +3854,19 @@
         <v>10.0</v>
       </c>
       <c r="H29" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="J29" s="1" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="K29" s="1">
         <v>120.0</v>
       </c>
       <c r="L29" s="1" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="P29" s="1" t="s">
-        <v>250</v>
+        <v>258</v>
       </c>
       <c r="Q29" s="1">
         <v>3.0</v>
@@ -3883,28 +3883,28 @@
     </row>
     <row r="30">
       <c r="A30" s="1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>255</v>
+        <v>262</v>
       </c>
       <c r="D30" s="1" t="b">
         <v>0</v>
       </c>
       <c r="H30" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="J30" s="1" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="L30" s="1" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="P30" s="1" t="s">
-        <v>258</v>
+        <v>265</v>
       </c>
       <c r="Q30" s="1">
         <v>4.0</v>
@@ -3921,13 +3921,13 @@
     </row>
     <row r="31">
       <c r="A31" s="1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>262</v>
+        <v>269</v>
       </c>
       <c r="D31" s="1" t="b">
         <v>0</v>
@@ -3937,19 +3937,19 @@
         <v>1.0</v>
       </c>
       <c r="H31" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="J31" s="1" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="K31" s="1">
         <v>10.0</v>
       </c>
       <c r="L31" s="1" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="P31" s="1" t="s">
-        <v>266</v>
+        <v>273</v>
       </c>
       <c r="Q31" s="1">
         <v>5.0</v>
@@ -3966,13 +3966,13 @@
     </row>
     <row r="32">
       <c r="A32" s="1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>269</v>
+        <v>277</v>
       </c>
       <c r="D32" s="1" t="b">
         <v>0</v>
@@ -3982,16 +3982,16 @@
         <v>30.0</v>
       </c>
       <c r="H32" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K32" s="1">
         <v>80.0</v>
       </c>
       <c r="L32" s="1" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="P32" s="1" t="s">
-        <v>272</v>
+        <v>281</v>
       </c>
       <c r="Q32" s="1">
         <v>1.0</v>
@@ -4043,123 +4043,123 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="E1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="I1" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="F1" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="H1" s="1" t="s">
+      <c r="J1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="I1" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="J1" s="1" t="s">
+      <c r="L1" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="N1" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="L1" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="M1" s="1" t="s">
+      <c r="P1" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q1" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="R1" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="S1" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="P1" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="Q1" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="R1" s="1" t="s">
+      <c r="T1" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="V1" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="W1" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="X1" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="U1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="V1" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="W1" s="1" t="s">
+      <c r="Y1" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="X1" s="1" t="s">
+      <c r="Z1" s="1" t="s">
         <v>45</v>
-      </c>
-      <c r="Y1" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="Z1" s="1" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="D2" s="1" t="b">
         <v>1</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="G2" s="1">
         <v>15.0</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="K2" s="1">
         <v>50.0</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="P2" s="1" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="Q2" s="1">
         <v>1.0</v>
@@ -4174,54 +4174,54 @@
         <v>1</v>
       </c>
       <c r="U2" s="1" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="V2" s="1" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="W2" s="1" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="Y2" s="1" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="D3" s="1" t="b">
         <v>1</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="G3" s="1">
         <v>15.0</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="K3" s="1">
         <v>60.0</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="P3" s="1" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="Q3" s="1">
         <v>1.0</v>
@@ -4236,57 +4236,57 @@
         <v>1</v>
       </c>
       <c r="U3" s="1" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="V3" s="1" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="W3" s="1" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="Y3" s="1" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="D4" s="1" t="b">
         <v>1</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="G4" s="1">
         <v>15.0</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="K4" s="1">
         <v>55.0</v>
       </c>
       <c r="L4" s="1" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="P4" s="1" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="Q4" s="1">
         <v>1.0</v>
@@ -4301,54 +4301,54 @@
         <v>1</v>
       </c>
       <c r="U4" s="1" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="V4" s="1" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="W4" s="1" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="Y4" s="1" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="D5" s="1" t="b">
         <v>1</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="G5" s="1">
         <v>15.0</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="K5" s="1">
         <v>55.0</v>
       </c>
       <c r="L5" s="1" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="P5" s="1" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="Q5" s="1">
         <v>1.0</v>
@@ -4363,51 +4363,51 @@
         <v>1</v>
       </c>
       <c r="U5" s="1" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="V5" s="1" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="W5" s="1" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="D6" s="1" t="b">
         <v>1</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="G6" s="1">
         <v>15.0</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="J6" s="1" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="K6" s="1">
         <v>55.0</v>
       </c>
       <c r="L6" s="1" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="P6" s="1" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="Q6" s="1">
         <v>1.0</v>
@@ -4422,42 +4422,42 @@
         <v>1</v>
       </c>
       <c r="U6" s="1" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="V6" s="1" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="W6" s="1" t="s">
-        <v>91</v>
+        <v>81</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="D7" s="1" t="b">
         <v>0</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="K7" s="1">
         <v>60.0</v>
       </c>
       <c r="L7" s="1" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="P7" s="1" t="s">
-        <v>97</v>
+        <v>85</v>
       </c>
       <c r="Q7" s="1">
         <v>2.0</v>
@@ -4472,45 +4472,45 @@
         <v>1</v>
       </c>
       <c r="U7" s="1" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="V7" s="1" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="W7" s="1" t="s">
-        <v>99</v>
+        <v>87</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>102</v>
+        <v>88</v>
       </c>
       <c r="D8" s="1" t="b">
         <v>0</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="J8" s="1" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="K8" s="1">
         <v>40.0</v>
       </c>
       <c r="L8" s="1" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>105</v>
+        <v>91</v>
       </c>
       <c r="P8" s="1" t="s">
-        <v>107</v>
+        <v>92</v>
       </c>
       <c r="Q8" s="1">
         <v>3.0</v>
@@ -4525,60 +4525,60 @@
         <v>1</v>
       </c>
       <c r="U8" s="1" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="V8" s="1" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="W8" s="1" t="s">
-        <v>109</v>
+        <v>94</v>
       </c>
       <c r="Y8" s="1" t="s">
-        <v>110</v>
+        <v>95</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>114</v>
+        <v>97</v>
       </c>
       <c r="D9" s="1" t="b">
         <v>1</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>115</v>
+        <v>99</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="G9" s="1">
         <v>20.0</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="I9" s="1">
         <v>3.0</v>
       </c>
       <c r="J9" s="1" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="K9" s="1">
         <v>30.0</v>
       </c>
       <c r="L9" s="1" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="N9" s="1" t="s">
-        <v>118</v>
+        <v>100</v>
       </c>
       <c r="P9" s="1" t="s">
-        <v>119</v>
+        <v>102</v>
       </c>
       <c r="Q9" s="1">
         <v>4.0</v>
@@ -4593,60 +4593,60 @@
         <v>1</v>
       </c>
       <c r="U9" s="1" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="V9" s="1" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="W9" s="1" t="s">
-        <v>122</v>
+        <v>103</v>
       </c>
       <c r="Y9" s="1" t="s">
-        <v>124</v>
+        <v>105</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>114</v>
+        <v>97</v>
       </c>
       <c r="D10" s="1" t="b">
         <v>1</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>115</v>
+        <v>99</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>127</v>
+        <v>107</v>
       </c>
       <c r="G10" s="1">
         <v>13.0</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="I10" s="1">
         <v>3.0</v>
       </c>
       <c r="J10" s="1" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="K10" s="1">
         <v>50.0</v>
       </c>
       <c r="L10" s="1" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="N10" s="1" t="s">
-        <v>129</v>
+        <v>109</v>
       </c>
       <c r="P10" s="1" t="s">
-        <v>130</v>
+        <v>110</v>
       </c>
       <c r="Q10" s="1">
         <v>4.0</v>
@@ -4661,60 +4661,60 @@
         <v>1</v>
       </c>
       <c r="U10" s="1" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="V10" s="1" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="W10" s="1" t="s">
-        <v>132</v>
+        <v>112</v>
       </c>
       <c r="Y10" s="1" t="s">
-        <v>133</v>
+        <v>113</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>114</v>
+        <v>97</v>
       </c>
       <c r="D11" s="1" t="b">
         <v>1</v>
       </c>
       <c r="E11" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="F11" s="1" t="s">
         <v>115</v>
-      </c>
-      <c r="F11" s="1" t="s">
-        <v>136</v>
       </c>
       <c r="G11" s="1">
         <v>13.0</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="I11" s="1">
         <v>3.0</v>
       </c>
       <c r="J11" s="1" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="K11" s="1">
         <v>50.0</v>
       </c>
       <c r="L11" s="1" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="N11" s="1" t="s">
-        <v>139</v>
+        <v>116</v>
       </c>
       <c r="P11" s="1" t="s">
-        <v>130</v>
+        <v>110</v>
       </c>
       <c r="Q11" s="1">
         <v>4.0</v>
@@ -4729,60 +4729,60 @@
         <v>1</v>
       </c>
       <c r="U11" s="1" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="V11" s="1" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="W11" s="1" t="s">
-        <v>140</v>
+        <v>118</v>
       </c>
       <c r="Y11" s="1" t="s">
-        <v>141</v>
+        <v>119</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>114</v>
+        <v>97</v>
       </c>
       <c r="D12" s="1" t="b">
         <v>1</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>115</v>
+        <v>99</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>143</v>
+        <v>121</v>
       </c>
       <c r="G12" s="1">
         <v>13.0</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="I12" s="1">
         <v>3.0</v>
       </c>
       <c r="J12" s="1" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="K12" s="1">
         <v>50.0</v>
       </c>
       <c r="L12" s="1" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="N12" s="1" t="s">
-        <v>145</v>
+        <v>123</v>
       </c>
       <c r="P12" s="1" t="s">
-        <v>130</v>
+        <v>110</v>
       </c>
       <c r="Q12" s="1">
         <v>4.0</v>
@@ -4797,60 +4797,60 @@
         <v>1</v>
       </c>
       <c r="U12" s="1" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="V12" s="1" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="W12" s="1" t="s">
-        <v>146</v>
+        <v>125</v>
       </c>
       <c r="Y12" s="1" t="s">
-        <v>147</v>
+        <v>126</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>114</v>
+        <v>97</v>
       </c>
       <c r="D13" s="1" t="b">
         <v>1</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>115</v>
+        <v>99</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>149</v>
+        <v>127</v>
       </c>
       <c r="G13" s="1">
         <v>13.0</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="I13" s="1">
         <v>2.0</v>
       </c>
       <c r="J13" s="1" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="K13" s="1">
         <v>55.0</v>
       </c>
       <c r="L13" s="1" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="N13" s="1" t="s">
-        <v>151</v>
+        <v>129</v>
       </c>
       <c r="P13" s="1" t="s">
-        <v>130</v>
+        <v>110</v>
       </c>
       <c r="Q13" s="1">
         <v>4.0</v>
@@ -4865,60 +4865,60 @@
         <v>1</v>
       </c>
       <c r="U13" s="1" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="V13" s="1" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="W13" s="1" t="s">
-        <v>153</v>
+        <v>131</v>
       </c>
       <c r="Y13" s="1" t="s">
-        <v>154</v>
+        <v>132</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>114</v>
+        <v>97</v>
       </c>
       <c r="D14" s="1" t="b">
         <v>1</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>115</v>
+        <v>99</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>156</v>
+        <v>134</v>
       </c>
       <c r="G14" s="1">
         <v>13.0</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="I14" s="1">
         <v>3.0</v>
       </c>
       <c r="J14" s="1" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="K14" s="1">
         <v>45.0</v>
       </c>
       <c r="L14" s="1" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="N14" s="1" t="s">
-        <v>158</v>
+        <v>135</v>
       </c>
       <c r="P14" s="1" t="s">
-        <v>130</v>
+        <v>110</v>
       </c>
       <c r="Q14" s="1">
         <v>4.0</v>
@@ -4933,60 +4933,60 @@
         <v>1</v>
       </c>
       <c r="U14" s="1" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="V14" s="1" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="W14" s="1" t="s">
-        <v>160</v>
+        <v>137</v>
       </c>
       <c r="Y14" s="1" t="s">
-        <v>161</v>
+        <v>138</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>114</v>
+        <v>97</v>
       </c>
       <c r="D15" s="1" t="b">
         <v>1</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>115</v>
+        <v>99</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>163</v>
+        <v>140</v>
       </c>
       <c r="G15" s="1">
         <v>13.0</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="I15" s="1">
         <v>3.0</v>
       </c>
       <c r="J15" s="1" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="K15" s="1">
         <v>55.0</v>
       </c>
       <c r="L15" s="1" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="N15" s="1" t="s">
-        <v>164</v>
+        <v>141</v>
       </c>
       <c r="P15" s="1" t="s">
-        <v>130</v>
+        <v>110</v>
       </c>
       <c r="Q15" s="1">
         <v>4.0</v>
@@ -5001,57 +5001,57 @@
         <v>1</v>
       </c>
       <c r="U15" s="1" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="V15" s="1" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="W15" s="1" t="s">
-        <v>166</v>
+        <v>143</v>
       </c>
       <c r="Y15" s="1" t="s">
-        <v>167</v>
+        <v>144</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>169</v>
+        <v>145</v>
       </c>
       <c r="D16" s="1" t="b">
         <v>1</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>170</v>
+        <v>146</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>171</v>
+        <v>147</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="I16" s="1">
         <v>2.0</v>
       </c>
       <c r="J16" s="1" t="s">
-        <v>173</v>
+        <v>148</v>
       </c>
       <c r="K16" s="1">
         <v>40.0</v>
       </c>
       <c r="L16" s="1" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="N16" s="1" t="s">
-        <v>176</v>
+        <v>149</v>
       </c>
       <c r="P16" s="1" t="s">
-        <v>177</v>
+        <v>150</v>
       </c>
       <c r="Q16" s="1">
         <v>1.0</v>
@@ -5066,57 +5066,57 @@
         <v>1</v>
       </c>
       <c r="U16" s="1" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="V16" s="1" t="s">
-        <v>178</v>
+        <v>152</v>
       </c>
       <c r="W16" s="1" t="s">
-        <v>179</v>
+        <v>153</v>
       </c>
       <c r="Y16" s="1" t="s">
-        <v>182</v>
+        <v>154</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>169</v>
+        <v>145</v>
       </c>
       <c r="D17" s="1" t="b">
         <v>1</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>170</v>
+        <v>146</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>184</v>
+        <v>156</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="I17" s="1">
         <v>2.0</v>
       </c>
       <c r="J17" s="1" t="s">
-        <v>173</v>
+        <v>148</v>
       </c>
       <c r="K17" s="1">
         <v>40.0</v>
       </c>
       <c r="L17" s="1" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="N17" s="1" t="s">
-        <v>187</v>
+        <v>157</v>
       </c>
       <c r="P17" s="1" t="s">
-        <v>177</v>
+        <v>150</v>
       </c>
       <c r="Q17" s="1">
         <v>1.0</v>
@@ -5131,51 +5131,51 @@
         <v>1</v>
       </c>
       <c r="U17" s="1" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="V17" s="1" t="s">
-        <v>178</v>
+        <v>152</v>
       </c>
       <c r="W17" s="1" t="s">
-        <v>189</v>
+        <v>161</v>
       </c>
       <c r="Y17" s="1" t="s">
-        <v>190</v>
+        <v>162</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>193</v>
+        <v>165</v>
       </c>
       <c r="D18" s="1" t="b">
         <v>0</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="I18" s="1">
         <v>2.0</v>
       </c>
       <c r="J18" s="1" t="s">
-        <v>173</v>
+        <v>148</v>
       </c>
       <c r="K18" s="1">
         <v>40.0</v>
       </c>
       <c r="L18" s="1" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="N18" s="1" t="s">
-        <v>195</v>
+        <v>167</v>
       </c>
       <c r="P18" s="1" t="s">
-        <v>196</v>
+        <v>168</v>
       </c>
       <c r="Q18" s="1">
         <v>2.0</v>
@@ -5190,57 +5190,57 @@
         <v>1</v>
       </c>
       <c r="U18" s="1" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="V18" s="1" t="s">
-        <v>178</v>
+        <v>152</v>
       </c>
       <c r="W18" s="1" t="s">
-        <v>199</v>
+        <v>171</v>
       </c>
       <c r="Y18" s="1" t="s">
-        <v>200</v>
+        <v>172</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>202</v>
+        <v>175</v>
       </c>
       <c r="D19" s="1" t="b">
         <v>1</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>202</v>
+        <v>175</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>204</v>
+        <v>176</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="I19" s="1">
         <v>2.0</v>
       </c>
       <c r="J19" s="1" t="s">
-        <v>173</v>
+        <v>148</v>
       </c>
       <c r="K19" s="1">
         <v>40.0</v>
       </c>
       <c r="L19" s="1" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="N19" s="1" t="s">
-        <v>206</v>
+        <v>179</v>
       </c>
       <c r="P19" s="1" t="s">
-        <v>207</v>
+        <v>181</v>
       </c>
       <c r="Q19" s="1">
         <v>3.0</v>
@@ -5255,57 +5255,57 @@
         <v>1</v>
       </c>
       <c r="U19" s="1" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="V19" s="1" t="s">
-        <v>178</v>
+        <v>152</v>
       </c>
       <c r="W19" s="1" t="s">
-        <v>209</v>
+        <v>184</v>
       </c>
       <c r="Y19" s="1" t="s">
-        <v>210</v>
+        <v>185</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>202</v>
+        <v>175</v>
       </c>
       <c r="D20" s="1" t="b">
         <v>1</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>202</v>
+        <v>175</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>213</v>
+        <v>188</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="I20" s="1">
         <v>2.0</v>
       </c>
       <c r="J20" s="1" t="s">
-        <v>173</v>
+        <v>148</v>
       </c>
       <c r="K20" s="1">
         <v>40.0</v>
       </c>
       <c r="L20" s="1" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="N20" s="1" t="s">
-        <v>215</v>
+        <v>192</v>
       </c>
       <c r="P20" s="1" t="s">
-        <v>207</v>
+        <v>181</v>
       </c>
       <c r="Q20" s="1">
         <v>3.0</v>
@@ -5320,51 +5320,51 @@
         <v>1</v>
       </c>
       <c r="U20" s="1" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="V20" s="1" t="s">
-        <v>178</v>
+        <v>152</v>
       </c>
       <c r="W20" s="1" t="s">
-        <v>218</v>
+        <v>197</v>
       </c>
       <c r="Y20" s="1" t="s">
-        <v>219</v>
+        <v>199</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>220</v>
+        <v>202</v>
       </c>
       <c r="D21" s="1" t="b">
         <v>0</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="I21" s="1">
         <v>2.0</v>
       </c>
       <c r="J21" s="1" t="s">
-        <v>173</v>
+        <v>148</v>
       </c>
       <c r="K21" s="1">
         <v>40.0</v>
       </c>
       <c r="L21" s="1" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="N21" s="1" t="s">
-        <v>223</v>
+        <v>205</v>
       </c>
       <c r="P21" s="1" t="s">
-        <v>224</v>
+        <v>207</v>
       </c>
       <c r="Q21" s="1">
         <v>4.0</v>
@@ -5379,51 +5379,51 @@
         <v>1</v>
       </c>
       <c r="U21" s="1" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="V21" s="1" t="s">
-        <v>178</v>
+        <v>152</v>
       </c>
       <c r="W21" s="1" t="s">
-        <v>226</v>
+        <v>210</v>
       </c>
       <c r="Y21" s="1" t="s">
-        <v>227</v>
+        <v>212</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>229</v>
+        <v>213</v>
       </c>
       <c r="D22" s="1" t="b">
         <v>0</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="I22" s="1">
         <v>2.0</v>
       </c>
       <c r="J22" s="1" t="s">
-        <v>173</v>
+        <v>148</v>
       </c>
       <c r="K22" s="1">
         <v>40.0</v>
       </c>
       <c r="L22" s="1" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="N22" s="1" t="s">
-        <v>231</v>
+        <v>217</v>
       </c>
       <c r="P22" s="1" t="s">
-        <v>233</v>
+        <v>218</v>
       </c>
       <c r="Q22" s="1">
         <v>5.0</v>
@@ -5438,54 +5438,54 @@
         <v>1</v>
       </c>
       <c r="U22" s="1" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="V22" s="1" t="s">
-        <v>178</v>
+        <v>152</v>
       </c>
       <c r="W22" s="1" t="s">
-        <v>235</v>
+        <v>220</v>
       </c>
       <c r="Y22" s="1" t="s">
-        <v>236</v>
+        <v>222</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>237</v>
+        <v>229</v>
       </c>
       <c r="D23" s="1" t="b">
         <v>0</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="I23" s="1">
         <v>2.0</v>
       </c>
       <c r="J23" s="1" t="s">
-        <v>173</v>
+        <v>148</v>
       </c>
       <c r="K23" s="1">
         <v>40.0</v>
       </c>
       <c r="L23" s="1" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="M23" s="1" t="s">
-        <v>240</v>
+        <v>232</v>
       </c>
       <c r="N23" s="1" t="s">
-        <v>242</v>
+        <v>233</v>
       </c>
       <c r="P23" s="1" t="s">
-        <v>243</v>
+        <v>234</v>
       </c>
       <c r="Q23" s="1">
         <v>6.0</v>
@@ -5500,54 +5500,54 @@
         <v>1</v>
       </c>
       <c r="U23" s="1" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="V23" s="1" t="s">
-        <v>178</v>
+        <v>152</v>
       </c>
       <c r="W23" s="1" t="s">
-        <v>244</v>
+        <v>236</v>
       </c>
       <c r="Y23" s="1" t="s">
-        <v>246</v>
+        <v>237</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>248</v>
+        <v>240</v>
       </c>
       <c r="D24" s="1" t="b">
         <v>0</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="I24" s="1">
         <v>2.0</v>
       </c>
       <c r="J24" s="1" t="s">
-        <v>173</v>
+        <v>148</v>
       </c>
       <c r="K24" s="1">
         <v>40.0</v>
       </c>
       <c r="L24" s="1" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="M24" s="1" t="s">
-        <v>249</v>
+        <v>242</v>
       </c>
       <c r="N24" s="1" t="s">
-        <v>251</v>
+        <v>243</v>
       </c>
       <c r="P24" s="1" t="s">
-        <v>252</v>
+        <v>244</v>
       </c>
       <c r="Q24" s="1">
         <v>7.0</v>
@@ -5562,51 +5562,51 @@
         <v>1</v>
       </c>
       <c r="U24" s="1" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="V24" s="1" t="s">
-        <v>178</v>
+        <v>152</v>
       </c>
       <c r="W24" s="1" t="s">
-        <v>254</v>
+        <v>247</v>
       </c>
       <c r="Y24" s="1" t="s">
-        <v>256</v>
+        <v>248</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>257</v>
+        <v>250</v>
       </c>
       <c r="D25" s="1" t="b">
         <v>0</v>
       </c>
       <c r="H25" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="I25" s="1">
         <v>2.0</v>
       </c>
       <c r="J25" s="1" t="s">
-        <v>173</v>
+        <v>148</v>
       </c>
       <c r="K25" s="1">
         <v>40.0</v>
       </c>
       <c r="L25" s="1" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="N25" s="1" t="s">
-        <v>260</v>
+        <v>252</v>
       </c>
       <c r="P25" s="1" t="s">
-        <v>261</v>
+        <v>253</v>
       </c>
       <c r="Q25" s="1">
         <v>8.0</v>
@@ -5621,51 +5621,51 @@
         <v>1</v>
       </c>
       <c r="U25" s="1" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="V25" s="1" t="s">
-        <v>178</v>
+        <v>152</v>
       </c>
       <c r="W25" s="1" t="s">
-        <v>263</v>
+        <v>256</v>
       </c>
       <c r="Y25" s="1" t="s">
-        <v>264</v>
+        <v>257</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>265</v>
+        <v>259</v>
       </c>
       <c r="D26" s="1" t="b">
         <v>0</v>
       </c>
       <c r="H26" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="I26" s="1">
         <v>2.0</v>
       </c>
       <c r="J26" s="1" t="s">
-        <v>173</v>
+        <v>148</v>
       </c>
       <c r="K26" s="1">
         <v>40.0</v>
       </c>
       <c r="L26" s="1" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="N26" s="1" t="s">
-        <v>267</v>
+        <v>261</v>
       </c>
       <c r="P26" s="1" t="s">
-        <v>268</v>
+        <v>263</v>
       </c>
       <c r="Q26" s="1">
         <v>9.0</v>
@@ -5680,51 +5680,51 @@
         <v>1</v>
       </c>
       <c r="U26" s="1" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="V26" s="1" t="s">
-        <v>178</v>
+        <v>152</v>
       </c>
       <c r="W26" s="1" t="s">
-        <v>270</v>
+        <v>264</v>
       </c>
       <c r="Y26" s="1" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>273</v>
+        <v>268</v>
       </c>
       <c r="D27" s="1" t="b">
         <v>0</v>
       </c>
       <c r="H27" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="I27" s="1">
         <v>2.0</v>
       </c>
       <c r="J27" s="1" t="s">
-        <v>173</v>
+        <v>148</v>
       </c>
       <c r="K27" s="1">
         <v>40.0</v>
       </c>
       <c r="L27" s="1" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="N27" s="1" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="P27" s="1" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="Q27" s="1">
         <v>10.0</v>
@@ -5739,54 +5739,54 @@
         <v>1</v>
       </c>
       <c r="U27" s="1" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="V27" s="1" t="s">
-        <v>178</v>
+        <v>152</v>
       </c>
       <c r="W27" s="1" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="Y27" s="1" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="D28" s="1" t="b">
         <v>0</v>
       </c>
       <c r="H28" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="I28" s="1">
         <v>2.0</v>
       </c>
       <c r="J28" s="1" t="s">
-        <v>173</v>
+        <v>148</v>
       </c>
       <c r="K28" s="1">
         <v>40.0</v>
       </c>
       <c r="L28" s="1" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="M28" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="N28" s="1" t="s">
         <v>279</v>
       </c>
-      <c r="N28" s="1" t="s">
+      <c r="P28" s="1" t="s">
         <v>280</v>
-      </c>
-      <c r="P28" s="1" t="s">
-        <v>281</v>
       </c>
       <c r="Q28" s="1">
         <v>11.0</v>
@@ -5801,10 +5801,10 @@
         <v>1</v>
       </c>
       <c r="U28" s="1" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="V28" s="1" t="s">
-        <v>178</v>
+        <v>152</v>
       </c>
       <c r="W28" s="1" t="s">
         <v>282</v>
@@ -5815,10 +5815,10 @@
     </row>
     <row r="29">
       <c r="A29" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="C29" s="1" t="s">
         <v>284</v>
@@ -5827,25 +5827,25 @@
         <v>0</v>
       </c>
       <c r="H29" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="I29" s="1">
         <v>2.0</v>
       </c>
       <c r="J29" s="1" t="s">
-        <v>173</v>
+        <v>148</v>
       </c>
       <c r="K29" s="1">
         <v>40.0</v>
       </c>
       <c r="L29" s="1" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="N29" s="1" t="s">
         <v>285</v>
       </c>
       <c r="P29" s="1" t="s">
-        <v>261</v>
+        <v>253</v>
       </c>
       <c r="Q29" s="1">
         <v>12.0</v>
@@ -5860,10 +5860,10 @@
         <v>1</v>
       </c>
       <c r="U29" s="1" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="V29" s="1" t="s">
-        <v>178</v>
+        <v>152</v>
       </c>
       <c r="W29" s="1" t="s">
         <v>286</v>
@@ -5874,10 +5874,10 @@
     </row>
     <row r="30">
       <c r="A30" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="C30" s="1" t="s">
         <v>288</v>
@@ -5886,19 +5886,19 @@
         <v>0</v>
       </c>
       <c r="H30" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="I30" s="1">
         <v>2.0</v>
       </c>
       <c r="J30" s="1" t="s">
-        <v>173</v>
+        <v>148</v>
       </c>
       <c r="K30" s="1">
         <v>40.0</v>
       </c>
       <c r="L30" s="1" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="N30" s="1" t="s">
         <v>289</v>
@@ -5919,10 +5919,10 @@
         <v>1</v>
       </c>
       <c r="U30" s="1" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="V30" s="1" t="s">
-        <v>178</v>
+        <v>152</v>
       </c>
       <c r="W30" s="1" t="s">
         <v>291</v>
@@ -5933,10 +5933,10 @@
     </row>
     <row r="31">
       <c r="A31" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="C31" s="1" t="s">
         <v>293</v>
@@ -5945,19 +5945,19 @@
         <v>0</v>
       </c>
       <c r="H31" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="I31" s="1">
         <v>2.0</v>
       </c>
       <c r="J31" s="1" t="s">
-        <v>173</v>
+        <v>148</v>
       </c>
       <c r="K31" s="1">
         <v>40.0</v>
       </c>
       <c r="L31" s="1" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="N31" s="1" t="s">
         <v>294</v>
@@ -5978,10 +5978,10 @@
         <v>1</v>
       </c>
       <c r="U31" s="1" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="V31" s="1" t="s">
-        <v>178</v>
+        <v>152</v>
       </c>
       <c r="W31" s="1" t="s">
         <v>296</v>
@@ -5992,10 +5992,10 @@
     </row>
     <row r="32">
       <c r="A32" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="C32" s="1" t="s">
         <v>298</v>
@@ -6004,19 +6004,19 @@
         <v>0</v>
       </c>
       <c r="H32" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="I32" s="1">
         <v>2.0</v>
       </c>
       <c r="J32" s="1" t="s">
-        <v>173</v>
+        <v>148</v>
       </c>
       <c r="K32" s="1">
         <v>40.0</v>
       </c>
       <c r="L32" s="1" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="N32" s="1" t="s">
         <v>299</v>
@@ -6037,10 +6037,10 @@
         <v>1</v>
       </c>
       <c r="U32" s="1" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="V32" s="1" t="s">
-        <v>178</v>
+        <v>152</v>
       </c>
       <c r="W32" s="1" t="s">
         <v>301</v>
@@ -6051,10 +6051,10 @@
     </row>
     <row r="33">
       <c r="A33" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="C33" s="1" t="s">
         <v>303</v>
@@ -6063,19 +6063,19 @@
         <v>0</v>
       </c>
       <c r="H33" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="I33" s="1">
         <v>2.0</v>
       </c>
       <c r="J33" s="1" t="s">
-        <v>173</v>
+        <v>148</v>
       </c>
       <c r="K33" s="1">
         <v>40.0</v>
       </c>
       <c r="L33" s="1" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="N33" s="1" t="s">
         <v>304</v>
@@ -6096,10 +6096,10 @@
         <v>1</v>
       </c>
       <c r="U33" s="1" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="V33" s="1" t="s">
-        <v>178</v>
+        <v>152</v>
       </c>
       <c r="W33" s="1" t="s">
         <v>306</v>
@@ -6110,10 +6110,10 @@
     </row>
     <row r="34">
       <c r="A34" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="C34" s="1" t="s">
         <v>308</v>
@@ -6122,19 +6122,19 @@
         <v>0</v>
       </c>
       <c r="H34" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="I34" s="1">
         <v>3.0</v>
       </c>
       <c r="J34" s="1" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="K34" s="1">
         <v>40.0</v>
       </c>
       <c r="L34" s="1" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="N34" s="1" t="s">
         <v>309</v>
@@ -6155,7 +6155,7 @@
         <v>1</v>
       </c>
       <c r="U34" s="1" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="V34" s="1" t="s">
         <v>311</v>
@@ -6169,10 +6169,10 @@
     </row>
     <row r="35">
       <c r="A35" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="C35" s="1" t="s">
         <v>314</v>
@@ -6181,19 +6181,19 @@
         <v>0</v>
       </c>
       <c r="H35" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="I35" s="1">
         <v>3.0</v>
       </c>
       <c r="J35" s="1" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="K35" s="1">
         <v>40.0</v>
       </c>
       <c r="L35" s="1" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="N35" s="1" t="s">
         <v>315</v>
@@ -6214,7 +6214,7 @@
         <v>1</v>
       </c>
       <c r="U35" s="1" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="V35" s="1" t="s">
         <v>311</v>
@@ -6228,10 +6228,10 @@
     </row>
     <row r="36">
       <c r="A36" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="C36" s="1" t="s">
         <v>319</v>
@@ -6246,19 +6246,19 @@
         <v>320</v>
       </c>
       <c r="H36" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="I36" s="1">
         <v>3.0</v>
       </c>
       <c r="J36" s="1" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="K36" s="1">
         <v>40.0</v>
       </c>
       <c r="L36" s="1" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="M36" s="1" t="s">
         <v>321</v>
@@ -6282,7 +6282,7 @@
         <v>1</v>
       </c>
       <c r="U36" s="1" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="V36" s="1" t="s">
         <v>311</v>
@@ -6296,10 +6296,10 @@
     </row>
     <row r="37">
       <c r="A37" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="C37" s="1" t="s">
         <v>319</v>
@@ -6311,22 +6311,22 @@
         <v>319</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>143</v>
+        <v>121</v>
       </c>
       <c r="H37" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="I37" s="1">
         <v>3.0</v>
       </c>
       <c r="J37" s="1" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="K37" s="1">
         <v>40.0</v>
       </c>
       <c r="L37" s="1" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="N37" s="1" t="s">
         <v>326</v>
@@ -6347,7 +6347,7 @@
         <v>1</v>
       </c>
       <c r="U37" s="1" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="V37" s="1" t="s">
         <v>311</v>
@@ -6361,10 +6361,10 @@
     </row>
     <row r="38">
       <c r="A38" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="C38" s="1" t="s">
         <v>319</v>
@@ -6376,22 +6376,22 @@
         <v>319</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>136</v>
+        <v>115</v>
       </c>
       <c r="H38" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="I38" s="1">
         <v>3.0</v>
       </c>
       <c r="J38" s="1" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="K38" s="1">
         <v>40.0</v>
       </c>
       <c r="L38" s="1" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="N38" s="1" t="s">
         <v>329</v>
@@ -6412,7 +6412,7 @@
         <v>1</v>
       </c>
       <c r="U38" s="1" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="V38" s="1" t="s">
         <v>311</v>
@@ -6426,37 +6426,37 @@
     </row>
     <row r="39">
       <c r="A39" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="D39" s="1" t="b">
         <v>0</v>
       </c>
       <c r="H39" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="I39" s="1">
         <v>3.0</v>
       </c>
       <c r="J39" s="1" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="K39" s="1">
         <v>40.0</v>
       </c>
       <c r="L39" s="1" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="N39" s="1" t="s">
         <v>332</v>
       </c>
       <c r="P39" s="1" t="s">
-        <v>121</v>
+        <v>111</v>
       </c>
       <c r="Q39" s="1">
         <v>4.0</v>
@@ -6471,7 +6471,7 @@
         <v>1</v>
       </c>
       <c r="U39" s="1" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="V39" s="1" t="s">
         <v>311</v>
@@ -6485,10 +6485,10 @@
     </row>
     <row r="40">
       <c r="A40" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="C40" s="1" t="s">
         <v>335</v>
@@ -6497,19 +6497,19 @@
         <v>0</v>
       </c>
       <c r="H40" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="I40" s="1">
         <v>3.0</v>
       </c>
       <c r="J40" s="1" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="K40" s="1">
         <v>40.0</v>
       </c>
       <c r="L40" s="1" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="N40" s="1" t="s">
         <v>336</v>
@@ -6530,7 +6530,7 @@
         <v>1</v>
       </c>
       <c r="U40" s="1" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="V40" s="1" t="s">
         <v>311</v>
@@ -6544,10 +6544,10 @@
     </row>
     <row r="41">
       <c r="A41" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="C41" s="1" t="s">
         <v>340</v>
@@ -6556,19 +6556,19 @@
         <v>0</v>
       </c>
       <c r="H41" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="I41" s="1">
         <v>3.0</v>
       </c>
       <c r="J41" s="1" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="K41" s="1">
         <v>40.0</v>
       </c>
       <c r="L41" s="1" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="N41" s="1" t="s">
         <v>341</v>
@@ -6589,7 +6589,7 @@
         <v>1</v>
       </c>
       <c r="U41" s="1" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="V41" s="1" t="s">
         <v>311</v>
@@ -6603,10 +6603,10 @@
     </row>
     <row r="42">
       <c r="A42" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="C42" s="1" t="s">
         <v>345</v>
@@ -6615,19 +6615,19 @@
         <v>0</v>
       </c>
       <c r="H42" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="I42" s="1">
         <v>3.0</v>
       </c>
       <c r="J42" s="1" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="K42" s="1">
         <v>40.0</v>
       </c>
       <c r="L42" s="1" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="N42" s="1" t="s">
         <v>346</v>
@@ -6648,7 +6648,7 @@
         <v>1</v>
       </c>
       <c r="U42" s="1" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="V42" s="1" t="s">
         <v>311</v>
@@ -6662,10 +6662,10 @@
     </row>
     <row r="43">
       <c r="A43" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="C43" s="1" t="s">
         <v>350</v>
@@ -6677,19 +6677,19 @@
         <v>350</v>
       </c>
       <c r="H43" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="I43" s="1">
         <v>3.0</v>
       </c>
       <c r="J43" s="1" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="K43" s="1">
         <v>40.0</v>
       </c>
       <c r="L43" s="1" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="N43" s="1" t="s">
         <v>351</v>
@@ -6710,7 +6710,7 @@
         <v>1</v>
       </c>
       <c r="U43" s="1" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="V43" s="1" t="s">
         <v>311</v>
@@ -6724,10 +6724,10 @@
     </row>
     <row r="44">
       <c r="A44" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="C44" s="1" t="s">
         <v>355</v>
@@ -6742,19 +6742,19 @@
         <v>356</v>
       </c>
       <c r="H44" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="I44" s="1">
         <v>3.0</v>
       </c>
       <c r="J44" s="1" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="K44" s="1">
         <v>40.0</v>
       </c>
       <c r="L44" s="1" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="N44" s="1" t="s">
         <v>357</v>
@@ -6775,7 +6775,7 @@
         <v>1</v>
       </c>
       <c r="U44" s="1" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="V44" s="1" t="s">
         <v>311</v>
@@ -6789,10 +6789,10 @@
     </row>
     <row r="45">
       <c r="A45" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="C45" s="1" t="s">
         <v>360</v>
@@ -6801,19 +6801,19 @@
         <v>0</v>
       </c>
       <c r="H45" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="I45" s="1">
         <v>3.0</v>
       </c>
       <c r="J45" s="1" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="K45" s="1">
         <v>40.0</v>
       </c>
       <c r="L45" s="1" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="N45" s="1" t="s">
         <v>361</v>
@@ -6834,7 +6834,7 @@
         <v>1</v>
       </c>
       <c r="U45" s="1" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="V45" s="1" t="s">
         <v>311</v>
@@ -6848,10 +6848,10 @@
     </row>
     <row r="46">
       <c r="A46" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="C46" s="1" t="s">
         <v>365</v>
@@ -6866,19 +6866,19 @@
         <v>367</v>
       </c>
       <c r="H46" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="I46" s="1">
         <v>3.0</v>
       </c>
       <c r="J46" s="1" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="K46" s="1">
         <v>40.0</v>
       </c>
       <c r="L46" s="1" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="N46" s="1" t="s">
         <v>368</v>
@@ -6899,7 +6899,7 @@
         <v>1</v>
       </c>
       <c r="U46" s="1" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="V46" s="1" t="s">
         <v>311</v>
@@ -6913,10 +6913,10 @@
     </row>
     <row r="47">
       <c r="A47" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="C47" s="1" t="s">
         <v>372</v>
@@ -6931,19 +6931,19 @@
         <v>373</v>
       </c>
       <c r="H47" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="I47" s="1">
         <v>3.0</v>
       </c>
       <c r="J47" s="1" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="K47" s="1">
         <v>40.0</v>
       </c>
       <c r="L47" s="1" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="N47" s="1" t="s">
         <v>374</v>
@@ -6964,7 +6964,7 @@
         <v>1</v>
       </c>
       <c r="U47" s="1" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="V47" s="1" t="s">
         <v>311</v>
@@ -6978,10 +6978,10 @@
     </row>
     <row r="48">
       <c r="A48" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="C48" s="1" t="s">
         <v>377</v>
@@ -6996,19 +6996,19 @@
         <v>379</v>
       </c>
       <c r="H48" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="I48" s="1">
         <v>4.0</v>
       </c>
       <c r="J48" s="1" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="K48" s="1">
         <v>50.0</v>
       </c>
       <c r="L48" s="1" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="N48" s="1" t="s">
         <v>380</v>
@@ -7029,7 +7029,7 @@
         <v>1</v>
       </c>
       <c r="U48" s="1" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="V48" s="1" t="s">
         <v>382</v>
@@ -7043,10 +7043,10 @@
     </row>
     <row r="49">
       <c r="A49" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="C49" s="1" t="s">
         <v>385</v>
@@ -7061,19 +7061,19 @@
         <v>386</v>
       </c>
       <c r="H49" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="I49" s="1">
         <v>4.0</v>
       </c>
       <c r="J49" s="1" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="K49" s="1">
         <v>50.0</v>
       </c>
       <c r="L49" s="1" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="N49" s="1" t="s">
         <v>387</v>
@@ -7094,7 +7094,7 @@
         <v>1</v>
       </c>
       <c r="U49" s="1" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="V49" s="1" t="s">
         <v>382</v>
@@ -7108,10 +7108,10 @@
     </row>
     <row r="50">
       <c r="A50" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="C50" s="1" t="s">
         <v>390</v>
@@ -7123,19 +7123,19 @@
         <v>10.0</v>
       </c>
       <c r="H50" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="I50" s="1">
         <v>2.0</v>
       </c>
       <c r="J50" s="1" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="K50" s="1">
         <v>50.0</v>
       </c>
       <c r="L50" s="1" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="N50" s="1" t="s">
         <v>391</v>
@@ -7156,7 +7156,7 @@
         <v>1</v>
       </c>
       <c r="U50" s="1" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="V50" s="1" t="s">
         <v>382</v>
@@ -7170,10 +7170,10 @@
     </row>
     <row r="51">
       <c r="A51" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="C51" s="1" t="s">
         <v>395</v>
@@ -7185,19 +7185,19 @@
         <v>10.0</v>
       </c>
       <c r="H51" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="I51" s="1">
         <v>2.0</v>
       </c>
       <c r="J51" s="1" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="K51" s="1">
         <v>50.0</v>
       </c>
       <c r="L51" s="1" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="N51" s="1" t="s">
         <v>396</v>
@@ -7218,7 +7218,7 @@
         <v>1</v>
       </c>
       <c r="U51" s="1" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="V51" s="1" t="s">
         <v>382</v>
@@ -7232,10 +7232,10 @@
     </row>
     <row r="52">
       <c r="A52" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="C52" s="1" t="s">
         <v>400</v>
@@ -7247,19 +7247,19 @@
         <v>10.0</v>
       </c>
       <c r="H52" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="I52" s="1">
         <v>2.0</v>
       </c>
       <c r="J52" s="1" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="K52" s="1">
         <v>50.0</v>
       </c>
       <c r="L52" s="1" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="N52" s="1" t="s">
         <v>401</v>
@@ -7280,7 +7280,7 @@
         <v>1</v>
       </c>
       <c r="U52" s="1" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="V52" s="1" t="s">
         <v>382</v>
@@ -7294,10 +7294,10 @@
     </row>
     <row r="53">
       <c r="A53" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="C53" s="1" t="s">
         <v>405</v>
@@ -7309,19 +7309,19 @@
         <v>10.0</v>
       </c>
       <c r="H53" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="I53" s="1">
         <v>2.0</v>
       </c>
       <c r="J53" s="1" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="K53" s="1">
         <v>50.0</v>
       </c>
       <c r="L53" s="1" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="N53" s="1" t="s">
         <v>406</v>
@@ -7342,7 +7342,7 @@
         <v>1</v>
       </c>
       <c r="U53" s="1" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="V53" s="1" t="s">
         <v>382</v>
@@ -7356,10 +7356,10 @@
     </row>
     <row r="54">
       <c r="A54" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="C54" s="1" t="s">
         <v>410</v>
@@ -7371,19 +7371,19 @@
         <v>10.0</v>
       </c>
       <c r="H54" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="I54" s="1">
         <v>2.0</v>
       </c>
       <c r="J54" s="1" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="K54" s="1">
         <v>50.0</v>
       </c>
       <c r="L54" s="1" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="N54" s="1" t="s">
         <v>411</v>
@@ -7404,7 +7404,7 @@
         <v>1</v>
       </c>
       <c r="U54" s="1" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="V54" s="1" t="s">
         <v>382</v>
@@ -7418,10 +7418,10 @@
     </row>
     <row r="55">
       <c r="A55" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="C55" s="1" t="s">
         <v>415</v>
@@ -7433,19 +7433,19 @@
         <v>6.0</v>
       </c>
       <c r="H55" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="I55" s="1">
         <v>2.0</v>
       </c>
       <c r="J55" s="1" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="K55" s="1">
         <v>50.0</v>
       </c>
       <c r="L55" s="1" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="N55" s="1" t="s">
         <v>416</v>
@@ -7466,7 +7466,7 @@
         <v>1</v>
       </c>
       <c r="U55" s="1" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="V55" s="1" t="s">
         <v>382</v>
@@ -7480,10 +7480,10 @@
     </row>
     <row r="56">
       <c r="A56" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="C56" s="1" t="s">
         <v>420</v>
@@ -7495,19 +7495,19 @@
         <v>6.0</v>
       </c>
       <c r="H56" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="I56" s="1">
         <v>2.0</v>
       </c>
       <c r="J56" s="1" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="K56" s="1">
         <v>50.0</v>
       </c>
       <c r="L56" s="1" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="N56" s="1" t="s">
         <v>421</v>
@@ -7528,7 +7528,7 @@
         <v>1</v>
       </c>
       <c r="U56" s="1" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="V56" s="1" t="s">
         <v>382</v>
@@ -7542,10 +7542,10 @@
     </row>
     <row r="57">
       <c r="A57" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>31</v>
+        <v>43</v>
       </c>
       <c r="C57" s="1" t="s">
         <v>425</v>
@@ -7557,19 +7557,19 @@
         <v>6.0</v>
       </c>
       <c r="H57" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="I57" s="1">
         <v>2.0</v>
       </c>
       <c r="J57" s="1" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="K57" s="1">
         <v>50.0</v>
       </c>
       <c r="L57" s="1" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="N57" s="1" t="s">
         <v>426</v>
@@ -7590,7 +7590,7 @@
         <v>1</v>
       </c>
       <c r="U57" s="1" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="V57" s="1" t="s">
         <v>428</v>
@@ -7604,10 +7604,10 @@
     </row>
     <row r="58">
       <c r="A58" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>31</v>
+        <v>43</v>
       </c>
       <c r="C58" s="1" t="s">
         <v>431</v>
@@ -7625,13 +7625,13 @@
         <v>2.0</v>
       </c>
       <c r="J58" s="1" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="K58" s="1">
         <v>50.0</v>
       </c>
       <c r="L58" s="1" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="N58" s="1" t="s">
         <v>433</v>
@@ -7652,7 +7652,7 @@
         <v>1</v>
       </c>
       <c r="U58" s="1" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="V58" s="1" t="s">
         <v>428</v>
@@ -7666,10 +7666,10 @@
     </row>
     <row r="59">
       <c r="A59" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>31</v>
+        <v>43</v>
       </c>
       <c r="C59" s="1" t="s">
         <v>437</v>
@@ -7687,13 +7687,13 @@
         <v>2.0</v>
       </c>
       <c r="J59" s="1" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="K59" s="1">
         <v>50.0</v>
       </c>
       <c r="L59" s="1" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="N59" s="1" t="s">
         <v>438</v>
@@ -7714,7 +7714,7 @@
         <v>1</v>
       </c>
       <c r="U59" s="1" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="V59" s="1" t="s">
         <v>428</v>
@@ -7728,10 +7728,10 @@
     </row>
     <row r="60">
       <c r="A60" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>31</v>
+        <v>43</v>
       </c>
       <c r="C60" s="1" t="s">
         <v>442</v>
@@ -7743,19 +7743,19 @@
         <v>6.0</v>
       </c>
       <c r="H60" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="I60" s="1">
         <v>2.0</v>
       </c>
       <c r="J60" s="1" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="K60" s="1">
         <v>50.0</v>
       </c>
       <c r="L60" s="1" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="N60" s="1" t="s">
         <v>443</v>
@@ -7776,7 +7776,7 @@
         <v>1</v>
       </c>
       <c r="U60" s="1" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="V60" s="1" t="s">
         <v>428</v>
@@ -7790,10 +7790,10 @@
     </row>
     <row r="61">
       <c r="A61" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>31</v>
+        <v>43</v>
       </c>
       <c r="C61" s="1" t="s">
         <v>447</v>
@@ -7805,19 +7805,19 @@
         <v>6.0</v>
       </c>
       <c r="H61" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="I61" s="1">
         <v>2.0</v>
       </c>
       <c r="J61" s="1" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="K61" s="1">
         <v>50.0</v>
       </c>
       <c r="L61" s="1" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="N61" s="1" t="s">
         <v>448</v>
@@ -7838,7 +7838,7 @@
         <v>1</v>
       </c>
       <c r="U61" s="1" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="V61" s="1" t="s">
         <v>428</v>
@@ -7852,10 +7852,10 @@
     </row>
     <row r="62">
       <c r="A62" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>31</v>
+        <v>43</v>
       </c>
       <c r="C62" s="1" t="s">
         <v>452</v>
@@ -7867,19 +7867,19 @@
         <v>8.0</v>
       </c>
       <c r="H62" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="I62" s="1">
         <v>3.0</v>
       </c>
       <c r="J62" s="1" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="K62" s="1">
         <v>50.0</v>
       </c>
       <c r="L62" s="1" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="N62" s="1" t="s">
         <v>453</v>
@@ -7900,7 +7900,7 @@
         <v>1</v>
       </c>
       <c r="U62" s="1" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="V62" s="1" t="s">
         <v>428</v>
@@ -7914,10 +7914,10 @@
     </row>
     <row r="63">
       <c r="A63" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>31</v>
+        <v>43</v>
       </c>
       <c r="C63" s="1" t="s">
         <v>457</v>
@@ -7929,19 +7929,19 @@
         <v>8.0</v>
       </c>
       <c r="H63" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="I63" s="1">
         <v>3.0</v>
       </c>
       <c r="J63" s="1" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="K63" s="1">
         <v>50.0</v>
       </c>
       <c r="L63" s="1" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="N63" s="1" t="s">
         <v>458</v>
@@ -7962,7 +7962,7 @@
         <v>1</v>
       </c>
       <c r="U63" s="1" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="V63" s="1" t="s">
         <v>428</v>
@@ -7976,10 +7976,10 @@
     </row>
     <row r="64">
       <c r="A64" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>31</v>
+        <v>43</v>
       </c>
       <c r="C64" s="1" t="s">
         <v>462</v>
@@ -7991,19 +7991,19 @@
         <v>8.0</v>
       </c>
       <c r="H64" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="I64" s="1">
         <v>3.0</v>
       </c>
       <c r="J64" s="1" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="K64" s="1">
         <v>50.0</v>
       </c>
       <c r="L64" s="1" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="N64" s="1" t="s">
         <v>463</v>
@@ -8024,7 +8024,7 @@
         <v>1</v>
       </c>
       <c r="U64" s="1" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="V64" s="1" t="s">
         <v>428</v>
@@ -8038,10 +8038,10 @@
     </row>
     <row r="65">
       <c r="A65" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>31</v>
+        <v>43</v>
       </c>
       <c r="C65" s="1" t="s">
         <v>467</v>
@@ -8053,19 +8053,19 @@
         <v>8.0</v>
       </c>
       <c r="H65" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="I65" s="1">
         <v>3.0</v>
       </c>
       <c r="J65" s="1" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="K65" s="1">
         <v>50.0</v>
       </c>
       <c r="L65" s="1" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="N65" s="1" t="s">
         <v>468</v>
@@ -8086,7 +8086,7 @@
         <v>1</v>
       </c>
       <c r="U65" s="1" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="V65" s="1" t="s">
         <v>428</v>
@@ -8100,10 +8100,10 @@
     </row>
     <row r="66">
       <c r="A66" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>31</v>
+        <v>43</v>
       </c>
       <c r="C66" s="1" t="s">
         <v>472</v>
@@ -8115,19 +8115,19 @@
         <v>8.0</v>
       </c>
       <c r="H66" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="I66" s="1">
         <v>3.0</v>
       </c>
       <c r="J66" s="1" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="K66" s="1">
         <v>50.0</v>
       </c>
       <c r="L66" s="1" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="N66" s="1" t="s">
         <v>473</v>
@@ -8148,7 +8148,7 @@
         <v>1</v>
       </c>
       <c r="U66" s="1" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="V66" s="1" t="s">
         <v>428</v>
@@ -8162,10 +8162,10 @@
     </row>
     <row r="67">
       <c r="A67" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>31</v>
+        <v>43</v>
       </c>
       <c r="C67" s="1" t="s">
         <v>477</v>
@@ -8177,19 +8177,19 @@
         <v>8.0</v>
       </c>
       <c r="H67" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="I67" s="1">
         <v>3.0</v>
       </c>
       <c r="J67" s="1" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="K67" s="1">
         <v>50.0</v>
       </c>
       <c r="L67" s="1" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="N67" s="1" t="s">
         <v>478</v>
@@ -8210,7 +8210,7 @@
         <v>1</v>
       </c>
       <c r="U67" s="1" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="V67" s="1" t="s">
         <v>428</v>
@@ -8224,10 +8224,10 @@
     </row>
     <row r="68">
       <c r="A68" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>31</v>
+        <v>43</v>
       </c>
       <c r="C68" s="1" t="s">
         <v>482</v>
@@ -8236,19 +8236,19 @@
         <v>0</v>
       </c>
       <c r="H68" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="I68" s="1">
         <v>2.0</v>
       </c>
       <c r="J68" s="1" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="K68" s="1">
         <v>50.0</v>
       </c>
       <c r="L68" s="1" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="N68" s="1" t="s">
         <v>483</v>
@@ -8269,7 +8269,7 @@
         <v>1</v>
       </c>
       <c r="U68" s="1" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="V68" s="1" t="s">
         <v>428</v>
@@ -8283,10 +8283,10 @@
     </row>
     <row r="69">
       <c r="A69" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>31</v>
+        <v>43</v>
       </c>
       <c r="C69" s="1" t="s">
         <v>487</v>
@@ -8295,19 +8295,19 @@
         <v>0</v>
       </c>
       <c r="H69" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="I69" s="1">
         <v>2.0</v>
       </c>
       <c r="J69" s="1" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="K69" s="1">
         <v>70.0</v>
       </c>
       <c r="L69" s="1" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="N69" s="1" t="s">
         <v>488</v>
@@ -8328,7 +8328,7 @@
         <v>1</v>
       </c>
       <c r="U69" s="1" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="V69" s="1" t="s">
         <v>428</v>
@@ -8342,10 +8342,10 @@
     </row>
     <row r="70">
       <c r="A70" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>31</v>
+        <v>43</v>
       </c>
       <c r="C70" s="1" t="s">
         <v>492</v>
@@ -8354,19 +8354,19 @@
         <v>0</v>
       </c>
       <c r="H70" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="I70" s="1">
         <v>2.0</v>
       </c>
       <c r="J70" s="1" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="K70" s="1">
         <v>60.0</v>
       </c>
       <c r="L70" s="1" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="N70" s="1" t="s">
         <v>493</v>
@@ -8387,7 +8387,7 @@
         <v>1</v>
       </c>
       <c r="U70" s="1" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="V70" s="1" t="s">
         <v>428</v>
@@ -8401,10 +8401,10 @@
     </row>
     <row r="71">
       <c r="A71" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>31</v>
+        <v>43</v>
       </c>
       <c r="C71" s="1" t="s">
         <v>497</v>
@@ -8413,19 +8413,19 @@
         <v>0</v>
       </c>
       <c r="H71" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="I71" s="1">
         <v>3.0</v>
       </c>
       <c r="J71" s="1" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="K71" s="1">
         <v>50.0</v>
       </c>
       <c r="L71" s="1" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="N71" s="1" t="s">
         <v>498</v>
@@ -8446,7 +8446,7 @@
         <v>1</v>
       </c>
       <c r="U71" s="1" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="V71" s="1" t="s">
         <v>428</v>
@@ -8460,10 +8460,10 @@
     </row>
     <row r="72">
       <c r="A72" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>31</v>
+        <v>43</v>
       </c>
       <c r="C72" s="1" t="s">
         <v>502</v>
@@ -8472,19 +8472,19 @@
         <v>0</v>
       </c>
       <c r="H72" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="I72" s="1">
         <v>4.0</v>
       </c>
       <c r="J72" s="1" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="K72" s="1">
         <v>70.0</v>
       </c>
       <c r="L72" s="1" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="N72" s="1" t="s">
         <v>503</v>
@@ -8505,7 +8505,7 @@
         <v>1</v>
       </c>
       <c r="U72" s="1" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="V72" s="1" t="s">
         <v>428</v>
@@ -8519,10 +8519,10 @@
     </row>
     <row r="73">
       <c r="A73" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="C73" s="1" t="s">
         <v>507</v>
@@ -8531,19 +8531,19 @@
         <v>0</v>
       </c>
       <c r="H73" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="I73" s="1">
         <v>4.0</v>
       </c>
       <c r="J73" s="1" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="K73" s="1">
         <v>60.0</v>
       </c>
       <c r="L73" s="1" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="N73" s="1" t="s">
         <v>508</v>
@@ -8564,7 +8564,7 @@
         <v>1</v>
       </c>
       <c r="U73" s="1" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="V73" s="1" t="s">
         <v>510</v>
@@ -8578,10 +8578,10 @@
     </row>
     <row r="74">
       <c r="A74" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="C74" s="1" t="s">
         <v>513</v>
@@ -8590,19 +8590,19 @@
         <v>0</v>
       </c>
       <c r="H74" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="I74" s="1">
         <v>4.0</v>
       </c>
       <c r="J74" s="1" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="K74" s="1">
         <v>35.0</v>
       </c>
       <c r="L74" s="1" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="N74" s="1" t="s">
         <v>514</v>
@@ -8623,7 +8623,7 @@
         <v>1</v>
       </c>
       <c r="U74" s="1" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="V74" s="1" t="s">
         <v>510</v>
@@ -8637,10 +8637,10 @@
     </row>
     <row r="75">
       <c r="A75" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="C75" s="1" t="s">
         <v>518</v>
@@ -8649,19 +8649,19 @@
         <v>0</v>
       </c>
       <c r="H75" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="I75" s="1">
         <v>4.0</v>
       </c>
       <c r="J75" s="1" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="K75" s="1">
         <v>30.0</v>
       </c>
       <c r="L75" s="1" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="N75" s="1" t="s">
         <v>519</v>
@@ -8682,7 +8682,7 @@
         <v>1</v>
       </c>
       <c r="U75" s="1" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="V75" s="1" t="s">
         <v>510</v>
@@ -8696,10 +8696,10 @@
     </row>
     <row r="76">
       <c r="A76" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="C76" s="1" t="s">
         <v>522</v>
@@ -8711,19 +8711,19 @@
         <v>12.0</v>
       </c>
       <c r="H76" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="I76" s="1">
         <v>4.0</v>
       </c>
       <c r="J76" s="1" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="K76" s="1">
         <v>50.0</v>
       </c>
       <c r="L76" s="1" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="N76" s="1" t="s">
         <v>523</v>
@@ -8744,7 +8744,7 @@
         <v>1</v>
       </c>
       <c r="U76" s="1" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="V76" s="1" t="s">
         <v>510</v>
@@ -8758,10 +8758,10 @@
     </row>
     <row r="77">
       <c r="A77" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="C77" s="1" t="s">
         <v>527</v>
@@ -8773,19 +8773,19 @@
         <v>12.0</v>
       </c>
       <c r="H77" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="I77" s="1">
         <v>4.0</v>
       </c>
       <c r="J77" s="1" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="K77" s="1">
         <v>50.0</v>
       </c>
       <c r="L77" s="1" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="N77" s="1" t="s">
         <v>528</v>
@@ -8806,7 +8806,7 @@
         <v>1</v>
       </c>
       <c r="U77" s="1" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="V77" s="1" t="s">
         <v>510</v>
@@ -8820,10 +8820,10 @@
     </row>
     <row r="78">
       <c r="A78" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="C78" s="1" t="s">
         <v>532</v>
@@ -8835,19 +8835,19 @@
         <v>12.0</v>
       </c>
       <c r="H78" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="I78" s="1">
         <v>4.0</v>
       </c>
       <c r="J78" s="1" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="K78" s="1">
         <v>50.0</v>
       </c>
       <c r="L78" s="1" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="N78" s="1" t="s">
         <v>533</v>
@@ -8868,7 +8868,7 @@
         <v>1</v>
       </c>
       <c r="U78" s="1" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="V78" s="1" t="s">
         <v>510</v>
@@ -8882,10 +8882,10 @@
     </row>
     <row r="79">
       <c r="A79" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="C79" s="1" t="s">
         <v>537</v>
@@ -8897,19 +8897,19 @@
         <v>6.0</v>
       </c>
       <c r="H79" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="I79" s="1">
         <v>3.0</v>
       </c>
       <c r="J79" s="1" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="K79" s="1">
         <v>50.0</v>
       </c>
       <c r="L79" s="1" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="N79" s="1" t="s">
         <v>538</v>
@@ -8930,7 +8930,7 @@
         <v>1</v>
       </c>
       <c r="U79" s="1" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="V79" s="1" t="s">
         <v>510</v>
@@ -8944,10 +8944,10 @@
     </row>
     <row r="80">
       <c r="A80" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="C80" s="1" t="s">
         <v>542</v>
@@ -8959,19 +8959,19 @@
         <v>6.0</v>
       </c>
       <c r="H80" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="I80" s="1">
         <v>3.0</v>
       </c>
       <c r="J80" s="1" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="K80" s="1">
         <v>50.0</v>
       </c>
       <c r="L80" s="1" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="N80" s="1" t="s">
         <v>538</v>
@@ -8992,7 +8992,7 @@
         <v>1</v>
       </c>
       <c r="U80" s="1" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="V80" s="1" t="s">
         <v>510</v>
@@ -9006,10 +9006,10 @@
     </row>
     <row r="81">
       <c r="A81" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="C81" s="1" t="s">
         <v>545</v>
@@ -9018,19 +9018,19 @@
         <v>0</v>
       </c>
       <c r="H81" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="I81" s="1">
         <v>3.0</v>
       </c>
       <c r="J81" s="1" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="K81" s="1">
         <v>50.0</v>
       </c>
       <c r="L81" s="1" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="N81" s="1" t="s">
         <v>546</v>
@@ -9051,7 +9051,7 @@
         <v>1</v>
       </c>
       <c r="U81" s="1" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="V81" s="1" t="s">
         <v>510</v>
@@ -9065,10 +9065,10 @@
     </row>
     <row r="82">
       <c r="A82" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="C82" s="1" t="s">
         <v>550</v>
@@ -9077,19 +9077,19 @@
         <v>0</v>
       </c>
       <c r="H82" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="I82" s="1">
         <v>2.0</v>
       </c>
       <c r="J82" s="1" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="K82" s="1">
         <v>45.0</v>
       </c>
       <c r="L82" s="1" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="N82" s="1" t="s">
         <v>551</v>
@@ -9110,7 +9110,7 @@
         <v>1</v>
       </c>
       <c r="U82" s="1" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="V82" s="1" t="s">
         <v>510</v>
@@ -9124,10 +9124,10 @@
     </row>
     <row r="83">
       <c r="A83" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="C83" s="1" t="s">
         <v>555</v>
@@ -9136,19 +9136,19 @@
         <v>0</v>
       </c>
       <c r="H83" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="I83" s="1">
         <v>2.0</v>
       </c>
       <c r="J83" s="1" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="K83" s="1">
         <v>50.0</v>
       </c>
       <c r="L83" s="1" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="N83" s="1" t="s">
         <v>556</v>
@@ -9169,7 +9169,7 @@
         <v>1</v>
       </c>
       <c r="U83" s="1" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="V83" s="1" t="s">
         <v>510</v>
@@ -9183,10 +9183,10 @@
     </row>
     <row r="84">
       <c r="A84" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="C84" s="1" t="s">
         <v>560</v>
@@ -9195,19 +9195,19 @@
         <v>0</v>
       </c>
       <c r="H84" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="I84" s="1">
         <v>2.0</v>
       </c>
       <c r="J84" s="1" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="K84" s="1">
         <v>50.0</v>
       </c>
       <c r="L84" s="1" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="N84" s="1" t="s">
         <v>561</v>
@@ -9228,7 +9228,7 @@
         <v>1</v>
       </c>
       <c r="U84" s="1" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="V84" s="1" t="s">
         <v>510</v>
@@ -9242,10 +9242,10 @@
     </row>
     <row r="85">
       <c r="A85" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="C85" s="1" t="s">
         <v>565</v>
@@ -9254,19 +9254,19 @@
         <v>0</v>
       </c>
       <c r="H85" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="I85" s="1">
         <v>2.0</v>
       </c>
       <c r="J85" s="1" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="K85" s="1">
         <v>25.0</v>
       </c>
       <c r="L85" s="1" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="N85" s="1" t="s">
         <v>566</v>
@@ -9287,7 +9287,7 @@
         <v>1</v>
       </c>
       <c r="U85" s="1" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="V85" s="1" t="s">
         <v>568</v>
@@ -9301,10 +9301,10 @@
     </row>
     <row r="86">
       <c r="A86" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="C86" s="1" t="s">
         <v>571</v>
@@ -9313,19 +9313,19 @@
         <v>0</v>
       </c>
       <c r="H86" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="I86" s="1">
         <v>2.0</v>
       </c>
       <c r="J86" s="1" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="K86" s="1">
         <v>20.0</v>
       </c>
       <c r="L86" s="1" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="N86" s="1" t="s">
         <v>572</v>
@@ -9346,7 +9346,7 @@
         <v>1</v>
       </c>
       <c r="U86" s="1" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="V86" s="1" t="s">
         <v>568</v>
@@ -9360,10 +9360,10 @@
     </row>
     <row r="87">
       <c r="A87" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="C87" s="1" t="s">
         <v>576</v>
@@ -9372,19 +9372,19 @@
         <v>0</v>
       </c>
       <c r="H87" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="I87" s="1">
         <v>2.0</v>
       </c>
       <c r="J87" s="1" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="K87" s="1">
         <v>25.0</v>
       </c>
       <c r="L87" s="1" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="N87" s="1" t="s">
         <v>577</v>
@@ -9405,7 +9405,7 @@
         <v>1</v>
       </c>
       <c r="U87" s="1" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="V87" s="1" t="s">
         <v>568</v>
@@ -9419,10 +9419,10 @@
     </row>
     <row r="88">
       <c r="A88" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="C88" s="1" t="s">
         <v>580</v>
@@ -9431,19 +9431,19 @@
         <v>0</v>
       </c>
       <c r="H88" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="I88" s="1">
         <v>2.0</v>
       </c>
       <c r="J88" s="1" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="K88" s="1">
         <v>25.0</v>
       </c>
       <c r="L88" s="1" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="N88" s="1" t="s">
         <v>581</v>
@@ -9464,7 +9464,7 @@
         <v>1</v>
       </c>
       <c r="U88" s="1" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="V88" s="1" t="s">
         <v>568</v>
@@ -9478,10 +9478,10 @@
     </row>
     <row r="89">
       <c r="A89" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="C89" s="1" t="s">
         <v>585</v>
@@ -9490,19 +9490,19 @@
         <v>0</v>
       </c>
       <c r="H89" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="I89" s="1">
         <v>2.0</v>
       </c>
       <c r="J89" s="1" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="K89" s="1">
         <v>40.0</v>
       </c>
       <c r="L89" s="1" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="N89" s="1" t="s">
         <v>586</v>
@@ -9523,7 +9523,7 @@
         <v>1</v>
       </c>
       <c r="U89" s="1" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="V89" s="1" t="s">
         <v>568</v>
@@ -9537,10 +9537,10 @@
     </row>
     <row r="90">
       <c r="A90" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="C90" s="1" t="s">
         <v>590</v>
@@ -9549,19 +9549,19 @@
         <v>0</v>
       </c>
       <c r="H90" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="I90" s="1">
         <v>2.0</v>
       </c>
       <c r="J90" s="1" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="K90" s="1">
         <v>30.0</v>
       </c>
       <c r="L90" s="1" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="N90" s="1" t="s">
         <v>591</v>
@@ -9582,7 +9582,7 @@
         <v>1</v>
       </c>
       <c r="U90" s="1" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="V90" s="1" t="s">
         <v>568</v>
@@ -9596,10 +9596,10 @@
     </row>
     <row r="91">
       <c r="A91" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="C91" s="1" t="s">
         <v>595</v>
@@ -9611,19 +9611,19 @@
         <v>25.0</v>
       </c>
       <c r="H91" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="I91" s="1">
         <v>2.0</v>
       </c>
       <c r="J91" s="1" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="K91" s="1">
         <v>45.0</v>
       </c>
       <c r="L91" s="1" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="N91" s="1" t="s">
         <v>596</v>
@@ -9644,7 +9644,7 @@
         <v>1</v>
       </c>
       <c r="U91" s="1" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="V91" s="1" t="s">
         <v>598</v>
@@ -9658,10 +9658,10 @@
     </row>
     <row r="92">
       <c r="A92" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="C92" s="1" t="s">
         <v>601</v>
@@ -9673,19 +9673,19 @@
         <v>6.0</v>
       </c>
       <c r="H92" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="I92" s="1">
         <v>3.0</v>
       </c>
       <c r="J92" s="1" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="K92" s="1">
         <v>50.0</v>
       </c>
       <c r="L92" s="1" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="M92" s="1" t="s">
         <v>602</v>
@@ -9709,7 +9709,7 @@
         <v>1</v>
       </c>
       <c r="U92" s="1" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="V92" s="1" t="s">
         <v>598</v>
@@ -9723,10 +9723,10 @@
     </row>
     <row r="93">
       <c r="A93" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="C93" s="1" t="s">
         <v>607</v>
@@ -9741,19 +9741,19 @@
         <v>609</v>
       </c>
       <c r="H93" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="I93" s="1">
         <v>4.0</v>
       </c>
       <c r="J93" s="1" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="K93" s="1">
         <v>50.0</v>
       </c>
       <c r="L93" s="1" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="M93" s="1" t="s">
         <v>610</v>
@@ -9777,7 +9777,7 @@
         <v>1</v>
       </c>
       <c r="U93" s="1" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="V93" s="1" t="s">
         <v>598</v>
@@ -9791,10 +9791,10 @@
     </row>
     <row r="94">
       <c r="A94" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="C94" s="1" t="s">
         <v>615</v>
@@ -9806,22 +9806,22 @@
         <v>608</v>
       </c>
       <c r="F94" s="1" t="s">
-        <v>163</v>
+        <v>140</v>
       </c>
       <c r="H94" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="I94" s="1">
         <v>4.0</v>
       </c>
       <c r="J94" s="1" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="K94" s="1">
         <v>50.0</v>
       </c>
       <c r="L94" s="1" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="N94" s="1" t="s">
         <v>616</v>
@@ -9842,7 +9842,7 @@
         <v>1</v>
       </c>
       <c r="U94" s="1" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="V94" s="1" t="s">
         <v>598</v>
@@ -9856,10 +9856,10 @@
     </row>
     <row r="95">
       <c r="A95" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="C95" s="1" t="s">
         <v>619</v>
@@ -9874,19 +9874,19 @@
         <v>620</v>
       </c>
       <c r="H95" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="I95" s="1">
         <v>4.0</v>
       </c>
       <c r="J95" s="1" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="K95" s="1">
         <v>60.0</v>
       </c>
       <c r="L95" s="1" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="N95" s="1" t="s">
         <v>621</v>
@@ -9907,7 +9907,7 @@
         <v>1</v>
       </c>
       <c r="U95" s="1" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="V95" s="1" t="s">
         <v>598</v>
@@ -9921,10 +9921,10 @@
     </row>
     <row r="96">
       <c r="A96" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="C96" s="1" t="s">
         <v>624</v>
@@ -9933,16 +9933,16 @@
         <v>0</v>
       </c>
       <c r="H96" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="J96" s="1" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="K96" s="1">
         <v>25.0</v>
       </c>
       <c r="L96" s="1" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="N96" s="1" t="s">
         <v>625</v>
@@ -9963,7 +9963,7 @@
         <v>1</v>
       </c>
       <c r="U96" s="1" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="V96" s="1" t="s">
         <v>568</v>
@@ -9977,10 +9977,10 @@
     </row>
     <row r="97">
       <c r="A97" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="C97" s="1" t="s">
         <v>629</v>
@@ -9989,16 +9989,16 @@
         <v>0</v>
       </c>
       <c r="H97" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="J97" s="1" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="K97" s="1">
         <v>30.0</v>
       </c>
       <c r="L97" s="1" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="N97" s="1" t="s">
         <v>630</v>
@@ -10019,7 +10019,7 @@
         <v>1</v>
       </c>
       <c r="U97" s="1" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="V97" s="1" t="s">
         <v>568</v>
@@ -10033,10 +10033,10 @@
     </row>
     <row r="98">
       <c r="A98" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="C98" s="1" t="s">
         <v>633</v>
@@ -10048,19 +10048,19 @@
         <v>25.0</v>
       </c>
       <c r="H98" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="I98" s="1">
         <v>2.0</v>
       </c>
       <c r="J98" s="1" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="K98" s="1">
         <v>40.0</v>
       </c>
       <c r="L98" s="1" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="M98" s="1" t="s">
         <v>634</v>
@@ -10084,7 +10084,7 @@
         <v>1</v>
       </c>
       <c r="U98" s="1" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="V98" s="1" t="s">
         <v>598</v>
@@ -10121,87 +10121,87 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="E1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="I1" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="F1" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="H1" s="1" t="s">
+      <c r="J1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="I1" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="J1" s="1" t="s">
+      <c r="L1" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="N1" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="L1" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="M1" s="1" t="s">
+      <c r="P1" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q1" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="R1" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="S1" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="P1" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="Q1" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="R1" s="1" t="s">
+      <c r="T1" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="V1" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="W1" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="X1" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="U1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="V1" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="W1" s="1" t="s">
+      <c r="Y1" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="X1" s="1" t="s">
+      <c r="Z1" s="1" t="s">
         <v>45</v>
-      </c>
-      <c r="Y1" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="Z1" s="1" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>78</v>
+        <v>159</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>79</v>
+        <v>160</v>
       </c>
       <c r="D2" s="1" t="b">
         <v>0</v>
@@ -10211,16 +10211,16 @@
         <v>20.0</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K2" s="1">
         <v>100.0</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="P2" s="1" t="s">
-        <v>81</v>
+        <v>164</v>
       </c>
       <c r="Q2" s="1">
         <v>1.0</v>
@@ -10237,10 +10237,10 @@
     </row>
     <row r="3">
       <c r="A3" s="1" t="s">
-        <v>78</v>
+        <v>159</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>85</v>
+        <v>166</v>
       </c>
       <c r="D3" s="1" t="b">
         <v>0</v>
@@ -10250,16 +10250,16 @@
         <v>20.0</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K3" s="1">
         <v>60.0</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="P3" s="1" t="s">
-        <v>87</v>
+        <v>170</v>
       </c>
       <c r="Q3" s="1">
         <v>2.0</v>
@@ -10276,10 +10276,10 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="s">
-        <v>78</v>
+        <v>159</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>89</v>
+        <v>174</v>
       </c>
       <c r="D4" s="1" t="b">
         <v>0</v>
@@ -10289,16 +10289,16 @@
         <v>20.0</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K4" s="1">
         <v>100.0</v>
       </c>
       <c r="L4" s="1" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="P4" s="1" t="s">
-        <v>93</v>
+        <v>177</v>
       </c>
       <c r="Q4" s="1">
         <v>3.0</v>
@@ -10315,10 +10315,10 @@
     </row>
     <row r="5">
       <c r="A5" s="1" t="s">
-        <v>78</v>
+        <v>159</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>95</v>
+        <v>180</v>
       </c>
       <c r="D5" s="1" t="b">
         <v>0</v>
@@ -10328,16 +10328,16 @@
         <v>20.0</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K5" s="1">
         <v>100.0</v>
       </c>
       <c r="L5" s="1" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="P5" s="1" t="s">
-        <v>98</v>
+        <v>183</v>
       </c>
       <c r="Q5" s="1">
         <v>4.0</v>
@@ -10354,10 +10354,10 @@
     </row>
     <row r="6">
       <c r="A6" s="1" t="s">
-        <v>78</v>
+        <v>159</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>103</v>
+        <v>186</v>
       </c>
       <c r="D6" s="1" t="b">
         <v>0</v>
@@ -10367,16 +10367,16 @@
         <v>20.0</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K6" s="1">
         <v>30.0</v>
       </c>
       <c r="L6" s="1" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="P6" s="1" t="s">
-        <v>104</v>
+        <v>190</v>
       </c>
       <c r="Q6" s="1">
         <v>5.0</v>
@@ -10393,10 +10393,10 @@
     </row>
     <row r="7">
       <c r="A7" s="1" t="s">
-        <v>78</v>
+        <v>159</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>108</v>
+        <v>194</v>
       </c>
       <c r="D7" s="1" t="b">
         <v>0</v>
@@ -10406,16 +10406,16 @@
         <v>20.0</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K7" s="1">
         <v>60.0</v>
       </c>
       <c r="L7" s="1" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="P7" s="1" t="s">
-        <v>113</v>
+        <v>198</v>
       </c>
       <c r="Q7" s="1">
         <v>6.0</v>
@@ -10432,10 +10432,10 @@
     </row>
     <row r="8">
       <c r="A8" s="1" t="s">
-        <v>78</v>
+        <v>159</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>116</v>
+        <v>203</v>
       </c>
       <c r="D8" s="1" t="b">
         <v>0</v>
@@ -10445,16 +10445,16 @@
         <v>20.0</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K8" s="1">
         <v>60.0</v>
       </c>
       <c r="L8" s="1" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="P8" s="1" t="s">
-        <v>120</v>
+        <v>206</v>
       </c>
       <c r="Q8" s="1">
         <v>7.0</v>
@@ -10471,10 +10471,10 @@
     </row>
     <row r="9">
       <c r="A9" s="1" t="s">
-        <v>78</v>
+        <v>159</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>123</v>
+        <v>209</v>
       </c>
       <c r="D9" s="1" t="b">
         <v>0</v>
@@ -10484,16 +10484,16 @@
         <v>20.0</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K9" s="1">
         <v>70.0</v>
       </c>
       <c r="L9" s="1" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="P9" s="1" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="Q9" s="1">
         <v>8.0</v>
@@ -10510,10 +10510,10 @@
     </row>
     <row r="10">
       <c r="A10" s="1" t="s">
-        <v>78</v>
+        <v>159</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>128</v>
+        <v>215</v>
       </c>
       <c r="D10" s="1" t="b">
         <v>0</v>
@@ -10523,16 +10523,16 @@
         <v>12.0</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K10" s="1">
         <v>70.0</v>
       </c>
       <c r="L10" s="1" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="P10" s="1" t="s">
-        <v>131</v>
+        <v>219</v>
       </c>
       <c r="Q10" s="1">
         <v>9.0</v>
@@ -10549,10 +10549,10 @@
     </row>
     <row r="11">
       <c r="A11" s="1" t="s">
-        <v>78</v>
+        <v>159</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>135</v>
+        <v>224</v>
       </c>
       <c r="D11" s="1" t="b">
         <v>0</v>
@@ -10562,16 +10562,16 @@
         <v>10.0</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K11" s="1">
         <v>70.0</v>
       </c>
       <c r="L11" s="1" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="P11" s="1" t="s">
-        <v>138</v>
+        <v>226</v>
       </c>
       <c r="Q11" s="1">
         <v>10.0</v>
@@ -10606,87 +10606,87 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="E1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="I1" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="F1" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="H1" s="1" t="s">
+      <c r="J1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="I1" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="J1" s="1" t="s">
+      <c r="L1" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="N1" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="L1" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="M1" s="1" t="s">
+      <c r="P1" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q1" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="R1" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="S1" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="P1" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="Q1" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="R1" s="1" t="s">
+      <c r="T1" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="V1" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="W1" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="X1" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="U1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="V1" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="W1" s="1" t="s">
+      <c r="Y1" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="X1" s="1" t="s">
+      <c r="Z1" s="1" t="s">
         <v>45</v>
-      </c>
-      <c r="Y1" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="Z1" s="1" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>174</v>
+        <v>189</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>175</v>
+        <v>191</v>
       </c>
       <c r="D2" s="1" t="b">
         <v>0</v>
@@ -10696,19 +10696,19 @@
         <v>20.0</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K2" s="1">
         <v>90.0</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>180</v>
+        <v>195</v>
       </c>
       <c r="P2" s="1" t="s">
-        <v>183</v>
+        <v>196</v>
       </c>
       <c r="Q2" s="1">
         <v>2.0</v>
@@ -10725,10 +10725,10 @@
     </row>
     <row r="3">
       <c r="A3" s="1" t="s">
-        <v>174</v>
+        <v>189</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>186</v>
+        <v>201</v>
       </c>
       <c r="D3" s="1" t="b">
         <v>0</v>
@@ -10738,19 +10738,19 @@
         <v>20.0</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K3" s="1">
         <v>90.0</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="M3" s="1" t="s">
-        <v>180</v>
+        <v>195</v>
       </c>
       <c r="P3" s="1" t="s">
-        <v>183</v>
+        <v>196</v>
       </c>
       <c r="Q3" s="1">
         <v>3.0</v>
@@ -10767,10 +10767,10 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="s">
-        <v>174</v>
+        <v>189</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>191</v>
+        <v>208</v>
       </c>
       <c r="D4" s="1" t="b">
         <v>0</v>
@@ -10780,19 +10780,19 @@
         <v>20.0</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K4" s="1">
         <v>90.0</v>
       </c>
       <c r="L4" s="1" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="M4" s="1" t="s">
-        <v>180</v>
+        <v>195</v>
       </c>
       <c r="P4" s="1" t="s">
-        <v>183</v>
+        <v>196</v>
       </c>
       <c r="Q4" s="1">
         <v>4.0</v>
@@ -10809,10 +10809,10 @@
     </row>
     <row r="5">
       <c r="A5" s="1" t="s">
-        <v>174</v>
+        <v>189</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>197</v>
+        <v>216</v>
       </c>
       <c r="D5" s="1" t="b">
         <v>0</v>
@@ -10822,19 +10822,19 @@
         <v>20.0</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K5" s="1">
         <v>90.0</v>
       </c>
       <c r="L5" s="1" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="M5" s="1" t="s">
-        <v>180</v>
+        <v>195</v>
       </c>
       <c r="P5" s="1" t="s">
-        <v>183</v>
+        <v>196</v>
       </c>
       <c r="Q5" s="1">
         <v>5.0</v>
@@ -10851,10 +10851,10 @@
     </row>
     <row r="6">
       <c r="A6" s="1" t="s">
-        <v>174</v>
+        <v>189</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>203</v>
+        <v>223</v>
       </c>
       <c r="D6" s="1" t="b">
         <v>0</v>
@@ -10864,19 +10864,19 @@
         <v>20.0</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K6" s="1">
         <v>90.0</v>
       </c>
       <c r="L6" s="1" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="M6" s="1" t="s">
-        <v>180</v>
+        <v>195</v>
       </c>
       <c r="P6" s="1" t="s">
-        <v>183</v>
+        <v>196</v>
       </c>
       <c r="Q6" s="1">
         <v>6.0</v>
@@ -10893,10 +10893,10 @@
     </row>
     <row r="7">
       <c r="A7" s="1" t="s">
-        <v>174</v>
+        <v>189</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>211</v>
+        <v>227</v>
       </c>
       <c r="D7" s="1" t="b">
         <v>0</v>
@@ -10906,19 +10906,19 @@
         <v>20.0</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K7" s="1">
         <v>90.0</v>
       </c>
       <c r="L7" s="1" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="M7" s="1" t="s">
-        <v>180</v>
+        <v>195</v>
       </c>
       <c r="P7" s="1" t="s">
-        <v>183</v>
+        <v>196</v>
       </c>
       <c r="Q7" s="1">
         <v>7.0</v>
@@ -10935,10 +10935,10 @@
     </row>
     <row r="8">
       <c r="A8" s="1" t="s">
-        <v>174</v>
+        <v>189</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>216</v>
+        <v>231</v>
       </c>
       <c r="D8" s="1" t="b">
         <v>0</v>
@@ -10948,19 +10948,19 @@
         <v>20.0</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K8" s="1">
         <v>90.0</v>
       </c>
       <c r="L8" s="1" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="M8" s="1" t="s">
-        <v>180</v>
+        <v>195</v>
       </c>
       <c r="P8" s="1" t="s">
-        <v>183</v>
+        <v>196</v>
       </c>
       <c r="Q8" s="1">
         <v>8.0</v>
@@ -10977,10 +10977,10 @@
     </row>
     <row r="9">
       <c r="A9" s="1" t="s">
-        <v>174</v>
+        <v>189</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>222</v>
+        <v>238</v>
       </c>
       <c r="D9" s="1" t="b">
         <v>0</v>
@@ -10989,19 +10989,19 @@
         <v>40.0</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K9" s="1">
         <v>170.0</v>
       </c>
       <c r="L9" s="1" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="M9" s="1" t="s">
-        <v>180</v>
+        <v>195</v>
       </c>
       <c r="P9" s="1" t="s">
-        <v>183</v>
+        <v>196</v>
       </c>
       <c r="Q9" s="1">
         <v>1.0</v>
@@ -11018,10 +11018,10 @@
     </row>
     <row r="10">
       <c r="A10" s="1" t="s">
-        <v>174</v>
+        <v>189</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>228</v>
+        <v>245</v>
       </c>
       <c r="D10" s="1" t="b">
         <v>0</v>
@@ -11030,16 +11030,16 @@
         <v>20.0</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K10" s="1">
         <v>90.0</v>
       </c>
       <c r="L10" s="1" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="P10" s="1" t="s">
-        <v>183</v>
+        <v>196</v>
       </c>
       <c r="Q10" s="1">
         <v>9.0</v>
@@ -11054,15 +11054,15 @@
         <v>1</v>
       </c>
       <c r="W10" s="1" t="s">
-        <v>232</v>
+        <v>249</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="s">
-        <v>174</v>
+        <v>189</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>228</v>
+        <v>245</v>
       </c>
       <c r="D11" s="1" t="b">
         <v>0</v>
@@ -11071,16 +11071,16 @@
         <v>20.0</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K11" s="1">
         <v>90.0</v>
       </c>
       <c r="L11" s="1" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="P11" s="1" t="s">
-        <v>183</v>
+        <v>196</v>
       </c>
       <c r="Q11" s="1">
         <v>10.0</v>
@@ -11095,15 +11095,15 @@
         <v>1</v>
       </c>
       <c r="W11" s="1" t="s">
-        <v>239</v>
+        <v>255</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="s">
-        <v>174</v>
+        <v>189</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>228</v>
+        <v>245</v>
       </c>
       <c r="D12" s="1" t="b">
         <v>0</v>
@@ -11112,16 +11112,16 @@
         <v>20.0</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K12" s="1">
         <v>90.0</v>
       </c>
       <c r="L12" s="1" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="P12" s="1" t="s">
-        <v>183</v>
+        <v>196</v>
       </c>
       <c r="Q12" s="1">
         <v>11.0</v>
@@ -11136,15 +11136,15 @@
         <v>1</v>
       </c>
       <c r="W12" s="1" t="s">
-        <v>247</v>
+        <v>260</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="s">
-        <v>174</v>
+        <v>189</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>228</v>
+        <v>245</v>
       </c>
       <c r="D13" s="1" t="b">
         <v>0</v>
@@ -11153,16 +11153,16 @@
         <v>20.0</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K13" s="1">
         <v>90.0</v>
       </c>
       <c r="L13" s="1" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="P13" s="1" t="s">
-        <v>183</v>
+        <v>196</v>
       </c>
       <c r="Q13" s="1">
         <v>12.0</v>
@@ -11177,15 +11177,15 @@
         <v>1</v>
       </c>
       <c r="W13" s="1" t="s">
-        <v>253</v>
+        <v>267</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="s">
-        <v>174</v>
+        <v>189</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>228</v>
+        <v>245</v>
       </c>
       <c r="D14" s="1" t="b">
         <v>0</v>
@@ -11194,16 +11194,16 @@
         <v>20.0</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K14" s="1">
         <v>90.0</v>
       </c>
       <c r="L14" s="1" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="P14" s="1" t="s">
-        <v>183</v>
+        <v>196</v>
       </c>
       <c r="Q14" s="1">
         <v>13.0</v>
@@ -11218,7 +11218,7 @@
         <v>1</v>
       </c>
       <c r="W14" s="1" t="s">
-        <v>259</v>
+        <v>272</v>
       </c>
     </row>
   </sheetData>
